--- a/outputs/northbound_aum_2026-04-29.xlsx
+++ b/outputs/northbound_aum_2026-04-29.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并成基金全称" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分各个份额（仅内地销售份额，不含所有份额）" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="合并成基金全称" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="分各个份额（仅内地销售份额，不含所有份额）" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'合并成基金全称'!$A$1:$T$45</definedName>
@@ -163,203 +163,203 @@
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东亚联丰投资管理
-抓取信息: Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202601_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202604_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FAPM_commentary_202603_EN_Final.pdf: Stream has ended unexpectedly</t>
+抓取信息: No manager source configured for 东亚联丰投资管理.</t>
       </text>
     </comment>
     <comment ref="J3" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 建银国际资管
-抓取信息: Link discovery failed for https://www.ccbintl.com.hk/English/management7.html: HTTPSConnectionPool(host='www.ccbintl.com.hk', port=443): Max retries exceeded with url: /English/management7.html (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1010)'))) | Fetch failed for https://www.ccbintl.com.hk/English/management7.html: HTTPSConnectionPool(host='www.ccbintl.com.hk', port=443): Max retries exceeded with url: /English/management7.html (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl</t>
+抓取信息: No manager source configured for 建银国际资管.</t>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 中银香港资管
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 中银香港资管.</t>
       </text>
     </comment>
     <comment ref="J5" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 中银香港资管
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 中银香港资管.</t>
       </text>
     </comment>
     <comment ref="J6" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 行健资管
-抓取信息: Link discovery failed for https://www.zealasset.com/en/about-us: HTTPSConnectionPool(host='www.zealasset.com', port=443): Max retries exceeded with url: /en/about-us (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1010)'))) | Fetch failed for https://www.zealasset.com/en/about-us: HTTPSConnectionPool(host='www.zealasset.com', port=443): Max retries exceeded with url: /en/about-us (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1010)'))) | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 行健资管.</t>
       </text>
     </comment>
     <comment ref="J7" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 中银保诚资管
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 中银保诚资管.</t>
       </text>
     </comment>
     <comment ref="J8" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 中银保诚资管
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 中银保诚资管.</t>
       </text>
     </comment>
     <comment ref="J9" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 恒生投资管理
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 恒生投资管理.</t>
       </text>
     </comment>
     <comment ref="J10" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J11" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J12" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 中银香港资管
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 中银香港资管.</t>
       </text>
     </comment>
     <comment ref="J13" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 施罗德投资管理(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 施罗德投资管理(香港).</t>
       </text>
     </comment>
     <comment ref="J14" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东方汇理(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 东方汇理(香港).</t>
       </text>
     </comment>
     <comment ref="J15" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 恒生投资管理
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 恒生投资管理.</t>
       </text>
     </comment>
     <comment ref="J16" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 惠理基金(香港).</t>
       </text>
     </comment>
     <comment ref="J17" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东亚联丰投资管理
-抓取信息: Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202601_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202604_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FAPM_commentary_202603_EN_Final.pdf: Stream has ended unexpectedly</t>
+抓取信息: No manager source configured for 东亚联丰投资管理.</t>
       </text>
     </comment>
     <comment ref="J18" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东方汇理(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 东方汇理(香港).</t>
       </text>
     </comment>
     <comment ref="J19" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J20" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J21" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J22" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 海通国际资管(香港)
-抓取信息: Link discovery failed for https://www.haitongetf.com.hk/asm/en-us: HTTPSConnectionPool(host='www.haitongetf.com.hk', port=443): Max retries exceeded with url: /asm/en-us (Caused by SSLError(SSLCertVerificationError(1, "[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: Hostname mismatch, certificate is not valid for 'www.haitongetf.com.hk'. (_ssl.c:1010)"))) | Fetch failed for https://www.haitongetf.com.hk/asm/en-us: HTTPSConnectionPool(host='www.haitongetf.com.hk', port=443): Max retries exceeded with url: /asm/en-us (Caused by SSLError(SSLCertVerificationError(1, "[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: Hostname mismatch, certificate is not valid for 'www.haito</t>
+抓取信息: No manager source configured for 海通国际资管(香港).</t>
       </text>
     </comment>
     <comment ref="J23" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J24" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 博时基金(国际)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 博时基金(国际).</t>
       </text>
     </comment>
     <comment ref="J25" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J26" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J27" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 惠理基金(香港).</t>
       </text>
     </comment>
     <comment ref="J28" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J29" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J30" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东方汇理(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 东方汇理(香港).</t>
       </text>
     </comment>
     <comment ref="J31" authorId="0" shapeId="0">
@@ -371,98 +371,98 @@
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 易方达资管(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 易方达资管(香港).</t>
       </text>
     </comment>
     <comment ref="J33" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 华夏基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 华夏基金(香港).</t>
       </text>
     </comment>
     <comment ref="J34" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 弘收资管(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 弘收资管(香港).</t>
       </text>
     </comment>
     <comment ref="J35" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 高腾国际资管
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 高腾国际资管.</t>
       </text>
     </comment>
     <comment ref="J36" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 兴证国际资管
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 兴证国际资管.</t>
       </text>
     </comment>
     <comment ref="J37" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 瑞银基金(卢森堡)
-抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 瑞银基金(卢森堡).</t>
       </text>
     </comment>
     <comment ref="J38" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东亚联丰投资管理
-抓取信息: Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202601_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202604_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FAPM_commentary_202603_EN_Final.pdf: Stream has ended unexpectedly</t>
+抓取信息: No manager source configured for 东亚联丰投资管理.</t>
       </text>
     </comment>
     <comment ref="J39" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 南方东英资管
-抓取信息: Link discovery failed for https://www.csopasset.com/: 403 Client Error: Forbidden for url: https://www.csopasset.com/ | Fetch failed for https://www.csopasset.com/: 403 Client Error: Forbidden for url: https://www.csopasset.com/ | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 南方东英资管.</t>
       </text>
     </comment>
     <comment ref="J40" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东亚联丰投资管理
-抓取信息: Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202601_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202604_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FAPM_commentary_202603_EN_Final.pdf: Stream has ended unexpectedly</t>
+抓取信息: No manager source configured for 东亚联丰投资管理.</t>
       </text>
     </comment>
     <comment ref="J41" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根资管(亚太)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根资管(亚太).</t>
       </text>
     </comment>
     <comment ref="J42" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东亚联丰投资管理
-抓取信息: Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202601_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202604_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FAPM_commentary_202603_EN_Final.pdf: Stream has ended unexpectedly</t>
+抓取信息: No manager source configured for 东亚联丰投资管理.</t>
       </text>
     </comment>
     <comment ref="J43" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东方汇理(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 东方汇理(香港).</t>
       </text>
     </comment>
     <comment ref="J44" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东方汇理(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 东方汇理(香港).</t>
       </text>
     </comment>
     <comment ref="J45" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
   </commentList>
@@ -479,441 +479,441 @@
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J3" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J5" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J6" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 行健资管
-抓取信息: Link discovery failed for https://www.zealasset.com/en/about-us: HTTPSConnectionPool(host='www.zealasset.com', port=443): Max retries exceeded with url: /en/about-us (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1010)'))) | Fetch failed for https://www.zealasset.com/en/about-us: HTTPSConnectionPool(host='www.zealasset.com', port=443): Max retries exceeded with url: /en/about-us (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1010)'))) | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 行健资管.</t>
       </text>
     </comment>
     <comment ref="J7" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 恒生投资管理
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 恒生投资管理.</t>
       </text>
     </comment>
     <comment ref="J8" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 恒生投资管理
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 恒生投资管理.</t>
       </text>
     </comment>
     <comment ref="J9" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 建银国际资管
-抓取信息: Link discovery failed for https://www.ccbintl.com.hk/English/management7.html: HTTPSConnectionPool(host='www.ccbintl.com.hk', port=443): Max retries exceeded with url: /English/management7.html (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1010)'))) | Fetch failed for https://www.ccbintl.com.hk/English/management7.html: HTTPSConnectionPool(host='www.ccbintl.com.hk', port=443): Max retries exceeded with url: /English/management7.html (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl</t>
+抓取信息: No manager source configured for 建银国际资管.</t>
       </text>
     </comment>
     <comment ref="J10" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J11" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J12" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 中银香港资管
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 中银香港资管.</t>
       </text>
     </comment>
     <comment ref="J13" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 施罗德投资管理(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 施罗德投资管理(香港).</t>
       </text>
     </comment>
     <comment ref="J14" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东方汇理(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 东方汇理(香港).</t>
       </text>
     </comment>
     <comment ref="J15" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东方汇理(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 东方汇理(香港).</t>
       </text>
     </comment>
     <comment ref="J16" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东亚联丰投资管理
-抓取信息: Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202601_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202604_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FAPM_commentary_202603_EN_Final.pdf: Stream has ended unexpectedly</t>
+抓取信息: No manager source configured for 东亚联丰投资管理.</t>
       </text>
     </comment>
     <comment ref="J17" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东亚联丰投资管理
-抓取信息: Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202601_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202604_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FAPM_commentary_202603_EN_Final.pdf: Stream has ended unexpectedly</t>
+抓取信息: No manager source configured for 东亚联丰投资管理.</t>
       </text>
     </comment>
     <comment ref="J18" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东亚联丰投资管理
-抓取信息: Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202601_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202604_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FAPM_commentary_202603_EN_Final.pdf: Stream has ended unexpectedly</t>
+抓取信息: No manager source configured for 东亚联丰投资管理.</t>
       </text>
     </comment>
     <comment ref="J19" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东亚联丰投资管理
-抓取信息: Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202601_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202604_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FAPM_commentary_202603_EN_Final.pdf: Stream has ended unexpectedly</t>
+抓取信息: No manager source configured for 东亚联丰投资管理.</t>
       </text>
     </comment>
     <comment ref="J20" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 中银保诚资管
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 中银保诚资管.</t>
       </text>
     </comment>
     <comment ref="J21" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东亚联丰投资管理
-抓取信息: Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202601_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202604_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FAPM_commentary_202603_EN_Final.pdf: Stream has ended unexpectedly</t>
+抓取信息: No manager source configured for 东亚联丰投资管理.</t>
       </text>
     </comment>
     <comment ref="J22" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 恒生投资管理
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 恒生投资管理.</t>
       </text>
     </comment>
     <comment ref="J23" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 中银保诚资管
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 中银保诚资管.</t>
       </text>
     </comment>
     <comment ref="J24" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 中银香港资管
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 中银香港资管.</t>
       </text>
     </comment>
     <comment ref="J25" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东方汇理(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 东方汇理(香港).</t>
       </text>
     </comment>
     <comment ref="J26" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东方汇理(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 东方汇理(香港).</t>
       </text>
     </comment>
     <comment ref="J27" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J28" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J29" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J30" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J31" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J32" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J33" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 惠理基金(香港).</t>
       </text>
     </comment>
     <comment ref="J34" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 惠理基金(香港).</t>
       </text>
     </comment>
     <comment ref="J35" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 惠理基金(香港).</t>
       </text>
     </comment>
     <comment ref="J36" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 惠理基金(香港).</t>
       </text>
     </comment>
     <comment ref="J37" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J38" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J39" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J40" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J41" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J42" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J43" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J44" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J45" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J46" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J47" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J48" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J49" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 海通国际资管(香港)
-抓取信息: Link discovery failed for https://www.haitongetf.com.hk/asm/en-us: HTTPSConnectionPool(host='www.haitongetf.com.hk', port=443): Max retries exceeded with url: /asm/en-us (Caused by SSLError(SSLCertVerificationError(1, "[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: Hostname mismatch, certificate is not valid for 'www.haitongetf.com.hk'. (_ssl.c:1010)"))) | Fetch failed for https://www.haitongetf.com.hk/asm/en-us: HTTPSConnectionPool(host='www.haitongetf.com.hk', port=443): Max retries exceeded with url: /asm/en-us (Caused by SSLError(SSLCertVerificationError(1, "[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: Hostname mismatch, certificate is not valid for 'www.haito</t>
+抓取信息: No manager source configured for 海通国际资管(香港).</t>
       </text>
     </comment>
     <comment ref="J50" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 博时基金(国际)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 博时基金(国际).</t>
       </text>
     </comment>
     <comment ref="J51" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 博时基金(国际)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 博时基金(国际).</t>
       </text>
     </comment>
     <comment ref="J52" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 博时基金(国际)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 博时基金(国际).</t>
       </text>
     </comment>
     <comment ref="J53" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 博时基金(国际)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 博时基金(国际).</t>
       </text>
     </comment>
     <comment ref="J54" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J55" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J56" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J57" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 惠理基金(香港).</t>
       </text>
     </comment>
     <comment ref="J58" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 惠理基金(香港).</t>
       </text>
     </comment>
     <comment ref="J59" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 惠理基金(香港).</t>
       </text>
     </comment>
     <comment ref="J60" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 惠理基金(香港).</t>
       </text>
     </comment>
     <comment ref="J61" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 惠理基金(香港).</t>
       </text>
     </comment>
     <comment ref="J62" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J63" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J64" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J65" authorId="0" shapeId="0">
@@ -930,469 +930,469 @@
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东方汇理(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 东方汇理(香港).</t>
       </text>
     </comment>
     <comment ref="J68" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东方汇理(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 东方汇理(香港).</t>
       </text>
     </comment>
     <comment ref="J69" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J70" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J71" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J72" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J73" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J74" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J75" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J76" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J77" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J78" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J79" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J80" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J81" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J82" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J83" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J84" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J85" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J86" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J87" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J88" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J89" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J90" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J91" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J92" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J93" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J94" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J95" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J96" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 海通国际资管(香港)
-抓取信息: Link discovery failed for https://www.haitongetf.com.hk/asm/en-us: HTTPSConnectionPool(host='www.haitongetf.com.hk', port=443): Max retries exceeded with url: /asm/en-us (Caused by SSLError(SSLCertVerificationError(1, "[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: Hostname mismatch, certificate is not valid for 'www.haitongetf.com.hk'. (_ssl.c:1010)"))) | Fetch failed for https://www.haitongetf.com.hk/asm/en-us: HTTPSConnectionPool(host='www.haitongetf.com.hk', port=443): Max retries exceeded with url: /asm/en-us (Caused by SSLError(SSLCertVerificationError(1, "[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: Hostname mismatch, certificate is not valid for 'www.haito</t>
+抓取信息: No manager source configured for 海通国际资管(香港).</t>
       </text>
     </comment>
     <comment ref="J97" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 海通国际资管(香港)
-抓取信息: Link discovery failed for https://www.haitongetf.com.hk/asm/en-us: HTTPSConnectionPool(host='www.haitongetf.com.hk', port=443): Max retries exceeded with url: /asm/en-us (Caused by SSLError(SSLCertVerificationError(1, "[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: Hostname mismatch, certificate is not valid for 'www.haitongetf.com.hk'. (_ssl.c:1010)"))) | Fetch failed for https://www.haitongetf.com.hk/asm/en-us: HTTPSConnectionPool(host='www.haitongetf.com.hk', port=443): Max retries exceeded with url: /asm/en-us (Caused by SSLError(SSLCertVerificationError(1, "[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: Hostname mismatch, certificate is not valid for 'www.haito</t>
+抓取信息: No manager source configured for 海通国际资管(香港).</t>
       </text>
     </comment>
     <comment ref="J98" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 华夏基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 华夏基金(香港).</t>
       </text>
     </comment>
     <comment ref="J99" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 华夏基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 华夏基金(香港).</t>
       </text>
     </comment>
     <comment ref="J100" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 华夏基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 华夏基金(香港).</t>
       </text>
     </comment>
     <comment ref="J101" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 易方达资管(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 易方达资管(香港).</t>
       </text>
     </comment>
     <comment ref="J102" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 易方达资管(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 易方达资管(香港).</t>
       </text>
     </comment>
     <comment ref="J103" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 易方达资管(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 易方达资管(香港).</t>
       </text>
     </comment>
     <comment ref="J104" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 弘收资管(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 弘收资管(香港).</t>
       </text>
     </comment>
     <comment ref="J105" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 弘收资管(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 弘收资管(香港).</t>
       </text>
     </comment>
     <comment ref="J106" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 弘收资管(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 弘收资管(香港).</t>
       </text>
     </comment>
     <comment ref="J107" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 弘收资管(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 弘收资管(香港).</t>
       </text>
     </comment>
     <comment ref="J108" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 高腾国际资管
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 高腾国际资管.</t>
       </text>
     </comment>
     <comment ref="J109" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 高腾国际资管
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 高腾国际资管.</t>
       </text>
     </comment>
     <comment ref="J110" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 高腾国际资管
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 高腾国际资管.</t>
       </text>
     </comment>
     <comment ref="J111" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 高腾国际资管
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 高腾国际资管.</t>
       </text>
     </comment>
     <comment ref="J112" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东亚联丰投资管理
-抓取信息: Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202601_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202604_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FAPM_commentary_202603_EN_Final.pdf: Stream has ended unexpectedly</t>
+抓取信息: No manager source configured for 东亚联丰投资管理.</t>
       </text>
     </comment>
     <comment ref="J113" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东亚联丰投资管理
-抓取信息: Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202601_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202604_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FAPM_commentary_202603_EN_Final.pdf: Stream has ended unexpectedly</t>
+抓取信息: No manager source configured for 东亚联丰投资管理.</t>
       </text>
     </comment>
     <comment ref="J114" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东亚联丰投资管理
-抓取信息: Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202601_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202604_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FAPM_commentary_202603_EN_Final.pdf: Stream has ended unexpectedly</t>
+抓取信息: No manager source configured for 东亚联丰投资管理.</t>
       </text>
     </comment>
     <comment ref="J115" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 兴证国际资管
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 兴证国际资管.</t>
       </text>
     </comment>
     <comment ref="J116" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 高腾国际资管
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 高腾国际资管.</t>
       </text>
     </comment>
     <comment ref="J117" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 高腾国际资管
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 高腾国际资管.</t>
       </text>
     </comment>
     <comment ref="J118" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 瑞银基金(卢森堡)
-抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 瑞银基金(卢森堡).</t>
       </text>
     </comment>
     <comment ref="J119" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 中银香港资管
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 中银香港资管.</t>
       </text>
     </comment>
     <comment ref="J120" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 南方东英资管
-抓取信息: Link discovery failed for https://www.csopasset.com/: 403 Client Error: Forbidden for url: https://www.csopasset.com/ | Fetch failed for https://www.csopasset.com/: 403 Client Error: Forbidden for url: https://www.csopasset.com/ | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 南方东英资管.</t>
       </text>
     </comment>
     <comment ref="J121" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 中银香港资管
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 中银香港资管.</t>
       </text>
     </comment>
     <comment ref="J122" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 中银香港资管
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 中银香港资管.</t>
       </text>
     </comment>
     <comment ref="J123" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东亚联丰投资管理
-抓取信息: Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202601_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202604_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FAPM_commentary_202603_EN_Final.pdf: Stream has ended unexpectedly</t>
+抓取信息: No manager source configured for 东亚联丰投资管理.</t>
       </text>
     </comment>
     <comment ref="J124" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东亚联丰投资管理
-抓取信息: Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202601_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202604_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FAPM_commentary_202603_EN_Final.pdf: Stream has ended unexpectedly</t>
+抓取信息: No manager source configured for 东亚联丰投资管理.</t>
       </text>
     </comment>
     <comment ref="J125" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根资管(亚太)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根资管(亚太).</t>
       </text>
     </comment>
     <comment ref="J126" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根资管(亚太)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根资管(亚太).</t>
       </text>
     </comment>
     <comment ref="J127" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根资管(亚太)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根资管(亚太).</t>
       </text>
     </comment>
     <comment ref="J128" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J129" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J130" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J131" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 施罗德投资管理(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 施罗德投资管理(香港).</t>
       </text>
     </comment>
     <comment ref="J132" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 施罗德投资管理(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 施罗德投资管理(香港).</t>
       </text>
     </comment>
     <comment ref="J133" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 施罗德投资管理(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 施罗德投资管理(香港).</t>
       </text>
     </comment>
     <comment ref="J134" authorId="0" shapeId="0">
@@ -1404,42 +1404,42 @@
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东亚联丰投资管理
-抓取信息: Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202601_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202604_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FAPM_commentary_202603_EN_Final.pdf: Stream has ended unexpectedly</t>
+抓取信息: No manager source configured for 东亚联丰投资管理.</t>
       </text>
     </comment>
     <comment ref="J136" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东亚联丰投资管理
-抓取信息: Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202601_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202604_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FAPM_commentary_202603_EN_Final.pdf: Stream has ended unexpectedly</t>
+抓取信息: No manager source configured for 东亚联丰投资管理.</t>
       </text>
     </comment>
     <comment ref="J137" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东方汇理(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 东方汇理(香港).</t>
       </text>
     </comment>
     <comment ref="J138" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东方汇理(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 东方汇理(香港).</t>
       </text>
     </comment>
     <comment ref="J139" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东方汇理(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 东方汇理(香港).</t>
       </text>
     </comment>
     <comment ref="J140" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东方汇理(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 东方汇理(香港).</t>
       </text>
     </comment>
     <comment ref="J141" authorId="0" shapeId="0">
@@ -1456,749 +1456,749 @@
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J144" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J145" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J146" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J147" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J148" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
       </text>
     </comment>
     <comment ref="J149" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东方汇理(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 东方汇理(香港).</t>
       </text>
     </comment>
     <comment ref="J150" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东方汇理(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 东方汇理(香港).</t>
       </text>
     </comment>
     <comment ref="J151" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东方汇理(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 东方汇理(香港).</t>
       </text>
     </comment>
     <comment ref="J152" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东方汇理(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 东方汇理(香港).</t>
       </text>
     </comment>
     <comment ref="J153" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东方汇理(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 东方汇理(香港).</t>
       </text>
     </comment>
     <comment ref="J154" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东方汇理(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 东方汇理(香港).</t>
       </text>
     </comment>
     <comment ref="J155" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东方汇理(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 东方汇理(香港).</t>
       </text>
     </comment>
     <comment ref="J156" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东方汇理(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 东方汇理(香港).</t>
       </text>
     </comment>
     <comment ref="J157" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 中银保诚资管
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 中银保诚资管.</t>
       </text>
     </comment>
     <comment ref="J158" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J159" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J160" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J161" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J162" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J163" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J164" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J165" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J166" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 摩根基金(亚洲).</t>
       </text>
     </comment>
     <comment ref="J167" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 安联环球投资(亚太)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 安联环球投资(亚太).</t>
       </text>
     </comment>
     <comment ref="J168" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 安联环球投资(亚太)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 安联环球投资(亚太).</t>
       </text>
     </comment>
     <comment ref="J169" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 安联环球投资(亚太)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 安联环球投资(亚太).</t>
       </text>
     </comment>
     <comment ref="J170" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 安联环球投资(亚太)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 安联环球投资(亚太).</t>
       </text>
     </comment>
     <comment ref="J171" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 安联环球投资(亚太)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 安联环球投资(亚太).</t>
       </text>
     </comment>
     <comment ref="J172" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 安联环球投资(亚太)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 安联环球投资(亚太).</t>
       </text>
     </comment>
     <comment ref="J173" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 安联环球投资(亚太)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 安联环球投资(亚太).</t>
       </text>
     </comment>
     <comment ref="J174" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 安联环球投资(亚太)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 安联环球投资(亚太).</t>
       </text>
     </comment>
     <comment ref="J175" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 安联环球投资(亚太)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 安联环球投资(亚太).</t>
       </text>
     </comment>
     <comment ref="J176" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 安联环球投资(亚太)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 安联环球投资(亚太).</t>
       </text>
     </comment>
     <comment ref="J177" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 安联环球投资(亚太)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 安联环球投资(亚太).</t>
       </text>
     </comment>
     <comment ref="J178" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 安联环球投资(亚太)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 安联环球投资(亚太).</t>
       </text>
     </comment>
     <comment ref="J179" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 安联环球投资(亚太)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 安联环球投资(亚太).</t>
       </text>
     </comment>
     <comment ref="J180" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 安联环球投资(亚太)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 安联环球投资(亚太).</t>
       </text>
     </comment>
     <comment ref="J181" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 华夏基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 华夏基金(香港).</t>
       </text>
     </comment>
     <comment ref="J182" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 华夏基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 华夏基金(香港).</t>
       </text>
     </comment>
     <comment ref="J183" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 华夏基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 华夏基金(香港).</t>
       </text>
     </comment>
     <comment ref="J184" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 华夏基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 华夏基金(香港).</t>
       </text>
     </comment>
     <comment ref="J185" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 华夏基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 华夏基金(香港).</t>
       </text>
     </comment>
     <comment ref="J186" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 华夏基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 华夏基金(香港).</t>
       </text>
     </comment>
     <comment ref="J187" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 华夏基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 华夏基金(香港).</t>
       </text>
     </comment>
     <comment ref="J188" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 华夏基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 华夏基金(香港).</t>
       </text>
     </comment>
     <comment ref="J189" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 华夏基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 华夏基金(香港).</t>
       </text>
     </comment>
     <comment ref="J190" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 华夏基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 华夏基金(香港).</t>
       </text>
     </comment>
     <comment ref="J191" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 华夏基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 华夏基金(香港).</t>
       </text>
     </comment>
     <comment ref="J192" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 华夏基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 华夏基金(香港).</t>
       </text>
     </comment>
     <comment ref="J193" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 华夏基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 华夏基金(香港).</t>
       </text>
     </comment>
     <comment ref="J194" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 华夏基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 华夏基金(香港).</t>
       </text>
     </comment>
     <comment ref="J195" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 华夏基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 华夏基金(香港).</t>
       </text>
     </comment>
     <comment ref="J196" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 华夏基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 华夏基金(香港).</t>
       </text>
     </comment>
     <comment ref="J197" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 华夏基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 华夏基金(香港).</t>
       </text>
     </comment>
     <comment ref="J198" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 华夏基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 华夏基金(香港).</t>
       </text>
     </comment>
     <comment ref="J199" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 华夏基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 华夏基金(香港).</t>
       </text>
     </comment>
     <comment ref="J200" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 华夏基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 华夏基金(香港).</t>
       </text>
     </comment>
     <comment ref="J201" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 贝莱德资管(北亚)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 贝莱德资管(北亚).</t>
       </text>
     </comment>
     <comment ref="J202" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 贝莱德资管(北亚)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 贝莱德资管(北亚).</t>
       </text>
     </comment>
     <comment ref="J203" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 贝莱德资管(北亚)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 贝莱德资管(北亚).</t>
       </text>
     </comment>
     <comment ref="J204" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 太平资管(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 太平资管(香港).</t>
       </text>
     </comment>
     <comment ref="J205" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 易方达资管(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 易方达资管(香港).</t>
       </text>
     </comment>
     <comment ref="J206" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 易方达资管(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 易方达资管(香港).</t>
       </text>
     </comment>
     <comment ref="J207" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 易方达资管(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 易方达资管(香港).</t>
       </text>
     </comment>
     <comment ref="J208" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 易方达资管(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 易方达资管(香港).</t>
       </text>
     </comment>
     <comment ref="J209" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 易方达资管(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 易方达资管(香港).</t>
       </text>
     </comment>
     <comment ref="J210" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 易方达资管(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 易方达资管(香港).</t>
       </text>
     </comment>
     <comment ref="J211" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 易方达资管(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 易方达资管(香港).</t>
       </text>
     </comment>
     <comment ref="J212" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 易方达资管(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 易方达资管(香港).</t>
       </text>
     </comment>
     <comment ref="J213" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 易方达资管(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 易方达资管(香港).</t>
       </text>
     </comment>
     <comment ref="J214" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 易方达资管(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 易方达资管(香港).</t>
       </text>
     </comment>
     <comment ref="J215" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 富达基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 富达基金(香港).</t>
       </text>
     </comment>
     <comment ref="J216" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 富达基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 富达基金(香港).</t>
       </text>
     </comment>
     <comment ref="J217" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 富达基金(香港)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No manager source configured for 富达基金(香港).</t>
       </text>
     </comment>
     <comment ref="J218" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 瑞银环球资管(香港)
-抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
       </text>
     </comment>
     <comment ref="J219" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 瑞银环球资管(香港)
-抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
       </text>
     </comment>
     <comment ref="J220" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 瑞银环球资管(香港)
-抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
       </text>
     </comment>
     <comment ref="J221" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 瑞银环球资管(香港)
-抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
       </text>
     </comment>
     <comment ref="J222" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 瑞银环球资管(香港)
-抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
       </text>
     </comment>
     <comment ref="J223" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 瑞银环球资管(香港)
-抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
       </text>
     </comment>
     <comment ref="J224" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 瑞银环球资管(香港)
-抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
       </text>
     </comment>
     <comment ref="J225" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 瑞银环球资管(香港)
-抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
       </text>
     </comment>
     <comment ref="J226" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 瑞银环球资管(香港)
-抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
       </text>
     </comment>
     <comment ref="J227" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 瑞银环球资管(香港)
-抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
       </text>
     </comment>
     <comment ref="J228" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 瑞银环球资管(香港)
-抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
       </text>
     </comment>
     <comment ref="J229" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 瑞银环球资管(香港)
-抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
       </text>
     </comment>
     <comment ref="J230" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 瑞银环球资管(香港)
-抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
       </text>
     </comment>
     <comment ref="J231" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 瑞银环球资管(香港)
-抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
       </text>
     </comment>
     <comment ref="J232" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 瑞银环球资管(香港)
-抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
       </text>
     </comment>
     <comment ref="J233" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 瑞银环球资管(香港)
-抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
       </text>
     </comment>
     <comment ref="J234" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 瑞银环球资管(香港)
-抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
       </text>
     </comment>
     <comment ref="J235" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 瑞银环球资管(香港)
-抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
       </text>
     </comment>
     <comment ref="J236" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 惠理基金(香港).</t>
       </text>
     </comment>
     <comment ref="J237" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 惠理基金(香港).</t>
       </text>
     </comment>
     <comment ref="J238" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 惠理基金(香港).</t>
       </text>
     </comment>
     <comment ref="J239" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 惠理基金(香港).</t>
       </text>
     </comment>
     <comment ref="J240" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 惠理基金(香港).</t>
       </text>
     </comment>
     <comment ref="J241" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 惠理基金(香港).</t>
       </text>
     </comment>
     <comment ref="J242" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 惠理基金(香港).</t>
       </text>
     </comment>
     <comment ref="J243" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 惠理基金(香港).</t>
       </text>
     </comment>
     <comment ref="J244" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 惠理基金(香港).</t>
       </text>
     </comment>
     <comment ref="J245" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 惠理基金(香港).</t>
       </text>
     </comment>
     <comment ref="J246" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 惠理基金(香港).</t>
       </text>
     </comment>
     <comment ref="J247" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 惠理基金(香港).</t>
       </text>
     </comment>
     <comment ref="J248" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 惠理基金(香港).</t>
       </text>
     </comment>
     <comment ref="J249" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
+抓取信息: No manager source configured for 惠理基金(香港).</t>
       </text>
     </comment>
   </commentList>

--- a/outputs/northbound_aum_2026-04-29.xlsx
+++ b/outputs/northbound_aum_2026-04-29.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并成基金全称" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分各个份额（仅内地销售份额，不含所有份额）" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="合并成基金全称" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="分各个份额（仅内地销售份额，不含所有份额）" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'合并成基金全称'!$A$1:$U$45</definedName>
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,6 +39,10 @@
     <font>
       <name val="Arial"/>
       <color rgb="00000000"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00FF0000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -66,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -77,6 +81,7 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -163,203 +168,205 @@
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东亚联丰投资管理
-抓取信息: No manager source configured for 东亚联丰投资管理.</t>
+抓取信息: Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202601_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202604_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FAPM_commentary_202603_EN_Final.pdf: Stream has ended unexpectedly</t>
       </text>
     </comment>
     <comment ref="K3" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 建银国际资管
-抓取信息: No manager source configured for 建银国际资管.</t>
+抓取信息: Link discovery failed for https://www.ccbintl.com.hk/English/management7.html: HTTPSConnectionPool(host='www.ccbintl.com.hk', port=443): Max retries exceeded with url: /English/management7.html (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1010)'))) | Fetch failed for https://www.ccbintl.com.hk/English/management7.html: HTTPSConnectionPool(host='www.ccbintl.com.hk', port=443): Max retries exceeded with url: /English/management7.html (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl</t>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 中银香港资管
-抓取信息: No manager source configured for 中银香港资管.</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K5" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 中银香港资管
-抓取信息: No manager source configured for 中银香港资管.</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K6" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 行健资管
-抓取信息: No manager source configured for 行健资管.</t>
+抓取信息: Link discovery failed for https://www.zealasset.com/en/about-us: HTTPSConnectionPool(host='www.zealasset.com', port=443): Max retries exceeded with url: /en/about-us (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1010)'))) | Fetch failed for https://www.zealasset.com/en/about-us: HTTPSConnectionPool(host='www.zealasset.com', port=443): Max retries exceeded with url: /en/about-us (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1010)'))) | No global fund AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K7" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 中银保诚资管
-抓取信息: No manager source configured for 中银保诚资管.</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K8" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 中银保诚资管
-抓取信息: No manager source configured for 中银保诚资管.</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K9" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 恒生投资管理
-抓取信息: No manager source configured for 恒生投资管理.</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K10" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K11" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K12" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 中银香港资管
-抓取信息: No manager source configured for 中银香港资管.</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K13" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 施罗德投资管理(香港)
-抓取信息: No manager source configured for 施罗德投资管理(香港).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K14" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东方汇理(香港)
-抓取信息: No manager source configured for 东方汇理(香港).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K15" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 恒生投资管理
-抓取信息: No manager source configured for 恒生投资管理.</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K16" authorId="0" shapeId="0">
       <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 惠理基金(香港)
-抓取信息: No manager source configured for 惠理基金(香港).</t>
+        <t>来源: 官网/财务报表自动抓取
+URL: https://www.valuepartners-group.com/en/products-services/funds/
+原币种: HKD
+上下文: iew Performance Download Factsheets Share Classes Currency Latest NAV Valuation date Morningstar Rating ISIN codes Bloomberg tickers Class A HKD HKD 105.63 27-04-2026 KYG9317M1033 VPCHIGC KY 2026-04-29 11:02:11 Class A USD USD 17.28 27-04-2026 KYG9317M1603 VPCHAUS KY 2026-04-29 11:02:16 Class A AUD Hedged AUD 15.90</t>
       </text>
     </comment>
     <comment ref="K17" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东亚联丰投资管理
-抓取信息: No manager source configured for 东亚联丰投资管理.</t>
+抓取信息: Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202601_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202604_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FAPM_commentary_202603_EN_Final.pdf: Stream has ended unexpectedly</t>
       </text>
     </comment>
     <comment ref="K18" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东方汇理(香港)
-抓取信息: No manager source configured for 东方汇理(香港).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K19" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K20" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K21" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K22" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 海通国际资管(香港)
-抓取信息: No manager source configured for 海通国际资管(香港).</t>
+抓取信息: Link discovery failed for https://www.haitongetf.com.hk/asm/en-us: HTTPSConnectionPool(host='www.haitongetf.com.hk', port=443): Max retries exceeded with url: /asm/en-us (Caused by SSLError(SSLCertVerificationError(1, "[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: Hostname mismatch, certificate is not valid for 'www.haitongetf.com.hk'. (_ssl.c:1010)"))) | Fetch failed for https://www.haitongetf.com.hk/asm/en-us: HTTPSConnectionPool(host='www.haitongetf.com.hk', port=443): Max retries exceeded with url: /asm/en-us (Caused by SSLError(SSLCertVerificationError(1, "[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: Hostname mismatch, certificate is not valid for 'www.haito</t>
       </text>
     </comment>
     <comment ref="K23" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K24" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 博时基金(国际)
-抓取信息: No manager source configured for 博时基金(国际).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K25" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K26" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K27" authorId="0" shapeId="0">
       <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 惠理基金(香港)
-抓取信息: No manager source configured for 惠理基金(香港).</t>
+        <t>来源: 官网/财务报表自动抓取
+URL: https://www.valuepartners-group.com/en/products-services/funds/
+原币种: EUR
+上下文: AD 3.16 27-04-2026 - KYG9319N2400 VPGCCAD KY 2026-04-29 11:03:33 Class A EUR Hedged MDis EUR 3.44 27-04-2026 - KYG9319N3499 VCHAMEH KY 2026-04-29 11:03:38 Class A EUR Hedged Acc EUR 6.80 27-04-2026 - KYG9319N3804 VPGAEHA KY 2026-04-29 11:03:37 Class A GBP He</t>
       </text>
     </comment>
     <comment ref="K28" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K29" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K30" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东方汇理(香港)
-抓取信息: No manager source configured for 东方汇理(香港).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K31" authorId="0" shapeId="0">
@@ -369,100 +376,101 @@
     </comment>
     <comment ref="K32" authorId="0" shapeId="0">
       <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 易方达资管(香港)
-抓取信息: No manager source configured for 易方达资管(香港).</t>
+        <t>来源: 官网/财务报表自动抓取
+URL: https://www.efunds.com.hk/aboutus
+原币种: USD
+上下文: Fund (HK) Select Bond Fund . Launched E Fund (HK) Greater China Leaders Fund . Launched E Fund (HK) Greater China Quality Growth Fund . 2013 Granted a quota of US$100 million by SAFE under the Qualified Foreign Institutional Investors (QFII) program. This made E Fund HK the first batch of wholly-owned subsidiaries of Chinese... Gran</t>
       </text>
     </comment>
     <comment ref="K33" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 华夏基金(香港)
-抓取信息: No manager source configured for 华夏基金(香港).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K34" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 弘收资管(香港)
-抓取信息: No manager source configured for 弘收资管(香港).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K35" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 高腾国际资管
-抓取信息: No manager source configured for 高腾国际资管.</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K36" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 兴证国际资管
-抓取信息: No manager source configured for 兴证国际资管.</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K37" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 瑞银基金(卢森堡)
-抓取信息: No manager source configured for 瑞银基金(卢森堡).</t>
+抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K38" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东亚联丰投资管理
-抓取信息: No manager source configured for 东亚联丰投资管理.</t>
+抓取信息: Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202601_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202604_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FAPM_commentary_202603_EN_Final.pdf: Stream has ended unexpectedly</t>
       </text>
     </comment>
     <comment ref="K39" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 南方东英资管
-抓取信息: No manager source configured for 南方东英资管.</t>
+抓取信息: Link discovery failed for https://www.csopasset.com/: 403 Client Error: Forbidden for url: https://www.csopasset.com/ | Fetch failed for https://www.csopasset.com/: 403 Client Error: Forbidden for url: https://www.csopasset.com/ | No global fund AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K40" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东亚联丰投资管理
-抓取信息: No manager source configured for 东亚联丰投资管理.</t>
+抓取信息: Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202601_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202604_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FAPM_commentary_202603_EN_Final.pdf: Stream has ended unexpectedly</t>
       </text>
     </comment>
     <comment ref="K41" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根资管(亚太)
-抓取信息: No manager source configured for 摩根资管(亚太).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K42" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东亚联丰投资管理
-抓取信息: No manager source configured for 东亚联丰投资管理.</t>
+抓取信息: Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202601_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202604_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FAPM_commentary_202603_EN_Final.pdf: Stream has ended unexpectedly</t>
       </text>
     </comment>
     <comment ref="K43" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东方汇理(香港)
-抓取信息: No manager source configured for 东方汇理(香港).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K44" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东方汇理(香港)
-抓取信息: No manager source configured for 东方汇理(香港).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K45" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
   </commentList>
@@ -479,1726 +487,1728 @@
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K3" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K5" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K6" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 行健资管
-抓取信息: No manager source configured for 行健资管.</t>
+抓取信息: Link discovery failed for https://www.zealasset.com/en/about-us: HTTPSConnectionPool(host='www.zealasset.com', port=443): Max retries exceeded with url: /en/about-us (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1010)'))) | Fetch failed for https://www.zealasset.com/en/about-us: HTTPSConnectionPool(host='www.zealasset.com', port=443): Max retries exceeded with url: /en/about-us (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1010)'))) | No global fund AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K7" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 恒生投资管理
-抓取信息: No manager source configured for 恒生投资管理.</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K8" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 恒生投资管理
-抓取信息: No manager source configured for 恒生投资管理.</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K9" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 建银国际资管
-抓取信息: No manager source configured for 建银国际资管.</t>
+抓取信息: Link discovery failed for https://www.ccbintl.com.hk/English/management7.html: HTTPSConnectionPool(host='www.ccbintl.com.hk', port=443): Max retries exceeded with url: /English/management7.html (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1010)'))) | Fetch failed for https://www.ccbintl.com.hk/English/management7.html: HTTPSConnectionPool(host='www.ccbintl.com.hk', port=443): Max retries exceeded with url: /English/management7.html (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl</t>
       </text>
     </comment>
     <comment ref="K10" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K11" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K12" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 中银香港资管
-抓取信息: No manager source configured for 中银香港资管.</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K13" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 施罗德投资管理(香港)
-抓取信息: No manager source configured for 施罗德投资管理(香港).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K14" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东方汇理(香港)
-抓取信息: No manager source configured for 东方汇理(香港).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K15" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东方汇理(香港)
-抓取信息: No manager source configured for 东方汇理(香港).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K16" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东亚联丰投资管理
-抓取信息: No manager source configured for 东亚联丰投资管理.</t>
+抓取信息: Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202601_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202604_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FAPM_commentary_202603_EN_Final.pdf: Stream has ended unexpectedly</t>
       </text>
     </comment>
     <comment ref="K17" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东亚联丰投资管理
-抓取信息: No manager source configured for 东亚联丰投资管理.</t>
+抓取信息: Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202601_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202604_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FAPM_commentary_202603_EN_Final.pdf: Stream has ended unexpectedly</t>
       </text>
     </comment>
     <comment ref="K18" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东亚联丰投资管理
-抓取信息: No manager source configured for 东亚联丰投资管理.</t>
+抓取信息: Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202601_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202604_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FAPM_commentary_202603_EN_Final.pdf: Stream has ended unexpectedly</t>
       </text>
     </comment>
     <comment ref="K19" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东亚联丰投资管理
-抓取信息: No manager source configured for 东亚联丰投资管理.</t>
+抓取信息: Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202601_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202604_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FAPM_commentary_202603_EN_Final.pdf: Stream has ended unexpectedly</t>
       </text>
     </comment>
     <comment ref="K20" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 中银保诚资管
-抓取信息: No manager source configured for 中银保诚资管.</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K21" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东亚联丰投资管理
-抓取信息: No manager source configured for 东亚联丰投资管理.</t>
+抓取信息: Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202601_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202604_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FAPM_commentary_202603_EN_Final.pdf: Stream has ended unexpectedly</t>
       </text>
     </comment>
     <comment ref="K22" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 恒生投资管理
-抓取信息: No manager source configured for 恒生投资管理.</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K23" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 中银保诚资管
-抓取信息: No manager source configured for 中银保诚资管.</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K24" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 中银香港资管
-抓取信息: No manager source configured for 中银香港资管.</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K25" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东方汇理(香港)
-抓取信息: No manager source configured for 东方汇理(香港).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K26" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 东方汇理(香港)
-抓取信息: No manager source configured for 东方汇理(香港).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K27" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K28" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K29" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K30" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K31" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K32" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K33" authorId="0" shapeId="0">
+      <text>
+        <t>来源: 官网/财务报表自动抓取
+URL: https://www.valuepartners-group.com/en/products-services/funds/
+原币种: HKD
+上下文: iew Performance Download Factsheets Share Classes Currency Latest NAV Valuation date Morningstar Rating ISIN codes Bloomberg tickers Class A HKD HKD 105.63 27-04-2026 KYG9317M1033 VPCHIGC KY 2026-04-29 11:02:11 Class A USD USD 17.28 27-04-2026 KYG9317M1603 VPCHAUS KY 2026-04-29 11:02:16 Class A AUD Hedged AUD 15.90</t>
+      </text>
+    </comment>
+    <comment ref="K34" authorId="0" shapeId="0">
+      <text>
+        <t>来源: 官网/财务报表自动抓取
+URL: https://www.valuepartners-group.com/en/products-services/funds/
+原币种: HKD
+上下文: iew Performance Download Factsheets Share Classes Currency Latest NAV Valuation date Morningstar Rating ISIN codes Bloomberg tickers Class A HKD HKD 105.63 27-04-2026 KYG9317M1033 VPCHIGC KY 2026-04-29 11:02:11 Class A USD USD 17.28 27-04-2026 KYG9317M1603 VPCHAUS KY 2026-04-29 11:02:16 Class A AUD Hedged AUD 15.90</t>
+      </text>
+    </comment>
+    <comment ref="K35" authorId="0" shapeId="0">
+      <text>
+        <t>来源: 官网/财务报表自动抓取
+URL: https://www.valuepartners-group.com/en/products-services/funds/
+原币种: HKD
+上下文: iew Performance Download Factsheets Share Classes Currency Latest NAV Valuation date Morningstar Rating ISIN codes Bloomberg tickers Class A HKD HKD 105.63 27-04-2026 KYG9317M1033 VPCHIGC KY 2026-04-29 11:02:11 Class A USD USD 17.28 27-04-2026 KYG9317M1603 VPCHAUS KY 2026-04-29 11:02:16 Class A AUD Hedged AUD 15.90</t>
+      </text>
+    </comment>
+    <comment ref="K36" authorId="0" shapeId="0">
+      <text>
+        <t>来源: 官网/财务报表自动抓取
+URL: https://www.valuepartners-group.com/en/products-services/funds/
+原币种: HKD
+上下文: iew Performance Download Factsheets Share Classes Currency Latest NAV Valuation date Morningstar Rating ISIN codes Bloomberg tickers Class A HKD HKD 105.63 27-04-2026 KYG9317M1033 VPCHIGC KY 2026-04-29 11:02:11 Class A USD USD 17.28 27-04-2026 KYG9317M1603 VPCHAUS KY 2026-04-29 11:02:16 Class A AUD Hedged AUD 15.90</t>
+      </text>
+    </comment>
+    <comment ref="K37" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 摩根基金(亚洲)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K38" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 摩根基金(亚洲)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K39" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 摩根基金(亚洲)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K40" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 摩根基金(亚洲)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K41" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 摩根基金(亚洲)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K42" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 摩根基金(亚洲)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K43" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 摩根基金(亚洲)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K44" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 摩根基金(亚洲)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K45" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 摩根基金(亚洲)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K46" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 摩根基金(亚洲)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K47" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 摩根基金(亚洲)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K48" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 摩根基金(亚洲)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K49" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 海通国际资管(香港)
+抓取信息: Link discovery failed for https://www.haitongetf.com.hk/asm/en-us: HTTPSConnectionPool(host='www.haitongetf.com.hk', port=443): Max retries exceeded with url: /asm/en-us (Caused by SSLError(SSLCertVerificationError(1, "[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: Hostname mismatch, certificate is not valid for 'www.haitongetf.com.hk'. (_ssl.c:1010)"))) | Fetch failed for https://www.haitongetf.com.hk/asm/en-us: HTTPSConnectionPool(host='www.haitongetf.com.hk', port=443): Max retries exceeded with url: /asm/en-us (Caused by SSLError(SSLCertVerificationError(1, "[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: Hostname mismatch, certificate is not valid for 'www.haito</t>
+      </text>
+    </comment>
+    <comment ref="K50" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 博时基金(国际)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K51" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 博时基金(国际)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K52" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 博时基金(国际)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K53" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 博时基金(国际)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K54" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 摩根基金(亚洲)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K55" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 摩根基金(亚洲)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K56" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 摩根基金(亚洲)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K57" authorId="0" shapeId="0">
+      <text>
+        <t>来源: 官网/财务报表自动抓取
+URL: https://www.valuepartners-group.com/en/products-services/funds/
+原币种: EUR
+上下文: AD 3.16 27-04-2026 - KYG9319N2400 VPGCCAD KY 2026-04-29 11:03:33 Class A EUR Hedged MDis EUR 3.44 27-04-2026 - KYG9319N3499 VCHAMEH KY 2026-04-29 11:03:38 Class A EUR Hedged Acc EUR 6.80 27-04-2026 - KYG9319N3804 VPGAEHA KY 2026-04-29 11:03:37 Class A GBP He</t>
+      </text>
+    </comment>
+    <comment ref="K58" authorId="0" shapeId="0">
+      <text>
+        <t>来源: 官网/财务报表自动抓取
+URL: https://www.valuepartners-group.com/en/products-services/funds/
+原币种: EUR
+上下文: AD 3.16 27-04-2026 - KYG9319N2400 VPGCCAD KY 2026-04-29 11:03:33 Class A EUR Hedged MDis EUR 3.44 27-04-2026 - KYG9319N3499 VCHAMEH KY 2026-04-29 11:03:38 Class A EUR Hedged Acc EUR 6.80 27-04-2026 - KYG9319N3804 VPGAEHA KY 2026-04-29 11:03:37 Class A GBP He</t>
+      </text>
+    </comment>
+    <comment ref="K59" authorId="0" shapeId="0">
+      <text>
+        <t>来源: 官网/财务报表自动抓取
+URL: https://www.valuepartners-group.com/en/products-services/funds/
+原币种: EUR
+上下文: AD 3.16 27-04-2026 - KYG9319N2400 VPGCCAD KY 2026-04-29 11:03:33 Class A EUR Hedged MDis EUR 3.44 27-04-2026 - KYG9319N3499 VCHAMEH KY 2026-04-29 11:03:38 Class A EUR Hedged Acc EUR 6.80 27-04-2026 - KYG9319N3804 VPGAEHA KY 2026-04-29 11:03:37 Class A GBP He</t>
+      </text>
+    </comment>
+    <comment ref="K60" authorId="0" shapeId="0">
+      <text>
+        <t>来源: 官网/财务报表自动抓取
+URL: https://www.valuepartners-group.com/en/products-services/funds/
+原币种: EUR
+上下文: AD 3.16 27-04-2026 - KYG9319N2400 VPGCCAD KY 2026-04-29 11:03:33 Class A EUR Hedged MDis EUR 3.44 27-04-2026 - KYG9319N3499 VCHAMEH KY 2026-04-29 11:03:38 Class A EUR Hedged Acc EUR 6.80 27-04-2026 - KYG9319N3804 VPGAEHA KY 2026-04-29 11:03:37 Class A GBP He</t>
+      </text>
+    </comment>
+    <comment ref="K61" authorId="0" shapeId="0">
+      <text>
+        <t>来源: 官网/财务报表自动抓取
+URL: https://www.valuepartners-group.com/en/products-services/funds/
+原币种: EUR
+上下文: AD 3.16 27-04-2026 - KYG9319N2400 VPGCCAD KY 2026-04-29 11:03:33 Class A EUR Hedged MDis EUR 3.44 27-04-2026 - KYG9319N3499 VCHAMEH KY 2026-04-29 11:03:38 Class A EUR Hedged Acc EUR 6.80 27-04-2026 - KYG9319N3804 VPGAEHA KY 2026-04-29 11:03:37 Class A GBP He</t>
+      </text>
+    </comment>
+    <comment ref="K62" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 摩根基金(亚洲)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K63" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 摩根基金(亚洲)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K64" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 摩根基金(亚洲)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K65" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。</t>
+      </text>
+    </comment>
+    <comment ref="K66" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。</t>
+      </text>
+    </comment>
+    <comment ref="K67" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 东方汇理(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K68" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 东方汇理(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K69" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 汇丰投资基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K70" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 汇丰投资基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K71" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 汇丰投资基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K72" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 汇丰投资基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K73" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 汇丰投资基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K74" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 汇丰投资基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K75" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 汇丰投资基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K76" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 汇丰投资基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K77" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 汇丰投资基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K78" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 汇丰投资基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K79" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 汇丰投资基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K80" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 汇丰投资基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K81" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 汇丰投资基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K82" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 汇丰投资基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K83" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 汇丰投资基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K84" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 汇丰投资基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K85" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 汇丰投资基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K86" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 汇丰投资基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K87" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 汇丰投资基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K88" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 汇丰投资基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K89" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 汇丰投资基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K90" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 汇丰投资基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K91" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 汇丰投资基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K92" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 汇丰投资基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K93" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 汇丰投资基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K94" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 汇丰投资基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K95" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 汇丰投资基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K96" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 海通国际资管(香港)
+抓取信息: Link discovery failed for https://www.haitongetf.com.hk/asm/en-us: HTTPSConnectionPool(host='www.haitongetf.com.hk', port=443): Max retries exceeded with url: /asm/en-us (Caused by SSLError(SSLCertVerificationError(1, "[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: Hostname mismatch, certificate is not valid for 'www.haitongetf.com.hk'. (_ssl.c:1010)"))) | Fetch failed for https://www.haitongetf.com.hk/asm/en-us: HTTPSConnectionPool(host='www.haitongetf.com.hk', port=443): Max retries exceeded with url: /asm/en-us (Caused by SSLError(SSLCertVerificationError(1, "[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: Hostname mismatch, certificate is not valid for 'www.haito</t>
+      </text>
+    </comment>
+    <comment ref="K97" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 海通国际资管(香港)
+抓取信息: Link discovery failed for https://www.haitongetf.com.hk/asm/en-us: HTTPSConnectionPool(host='www.haitongetf.com.hk', port=443): Max retries exceeded with url: /asm/en-us (Caused by SSLError(SSLCertVerificationError(1, "[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: Hostname mismatch, certificate is not valid for 'www.haitongetf.com.hk'. (_ssl.c:1010)"))) | Fetch failed for https://www.haitongetf.com.hk/asm/en-us: HTTPSConnectionPool(host='www.haitongetf.com.hk', port=443): Max retries exceeded with url: /asm/en-us (Caused by SSLError(SSLCertVerificationError(1, "[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: Hostname mismatch, certificate is not valid for 'www.haito</t>
+      </text>
+    </comment>
+    <comment ref="K98" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 华夏基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K99" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 华夏基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K100" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 华夏基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K101" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 易方达资管(香港)</t>
+      </text>
+    </comment>
+    <comment ref="K102" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 易方达资管(香港)</t>
+      </text>
+    </comment>
+    <comment ref="K103" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 易方达资管(香港)</t>
+      </text>
+    </comment>
+    <comment ref="K104" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 弘收资管(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K105" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 弘收资管(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K106" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 弘收资管(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K107" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 弘收资管(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K108" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 高腾国际资管
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K109" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 高腾国际资管
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K110" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 高腾国际资管
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K111" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 高腾国际资管
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K112" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 东亚联丰投资管理
+抓取信息: Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202601_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202604_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FAPM_commentary_202603_EN_Final.pdf: Stream has ended unexpectedly</t>
+      </text>
+    </comment>
+    <comment ref="K113" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 东亚联丰投资管理
+抓取信息: Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202601_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202604_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FAPM_commentary_202603_EN_Final.pdf: Stream has ended unexpectedly</t>
+      </text>
+    </comment>
+    <comment ref="K114" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 东亚联丰投资管理
+抓取信息: Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202601_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202604_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FAPM_commentary_202603_EN_Final.pdf: Stream has ended unexpectedly</t>
+      </text>
+    </comment>
+    <comment ref="K115" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 兴证国际资管
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K116" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 高腾国际资管
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K117" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 高腾国际资管
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K118" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 瑞银基金(卢森堡)
+抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K119" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 中银香港资管
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K120" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 南方东英资管
+抓取信息: Link discovery failed for https://www.csopasset.com/: 403 Client Error: Forbidden for url: https://www.csopasset.com/ | Fetch failed for https://www.csopasset.com/: 403 Client Error: Forbidden for url: https://www.csopasset.com/ | No global fund AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K121" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 中银香港资管
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K122" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 中银香港资管
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K123" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 东亚联丰投资管理
+抓取信息: Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202601_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202604_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FAPM_commentary_202603_EN_Final.pdf: Stream has ended unexpectedly</t>
+      </text>
+    </comment>
+    <comment ref="K124" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 东亚联丰投资管理
+抓取信息: Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202601_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202604_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FAPM_commentary_202603_EN_Final.pdf: Stream has ended unexpectedly</t>
+      </text>
+    </comment>
+    <comment ref="K125" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 摩根资管(亚太)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K126" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 摩根资管(亚太)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K127" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 摩根资管(亚太)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K128" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 摩根基金(亚洲)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K129" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 摩根基金(亚洲)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K130" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 摩根基金(亚洲)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K131" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 施罗德投资管理(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K132" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 施罗德投资管理(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K133" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 施罗德投资管理(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K134" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。</t>
+      </text>
+    </comment>
+    <comment ref="K135" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 东亚联丰投资管理
+抓取信息: Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202601_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202604_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FAPM_commentary_202603_EN_Final.pdf: Stream has ended unexpectedly</t>
+      </text>
+    </comment>
+    <comment ref="K136" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 东亚联丰投资管理
+抓取信息: Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202601_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FABC_commentary_202604_EN_Final.pdf: Stream has ended unexpectedly | Fetch failed for https://www.buim.com/get_pdf.php?pdf=images%2Fdata%2FFund_Commentary%2F2026%2FAPM_commentary_202603_EN_Final.pdf: Stream has ended unexpectedly</t>
+      </text>
+    </comment>
+    <comment ref="K137" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 东方汇理(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K138" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 东方汇理(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K139" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 东方汇理(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K140" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 东方汇理(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K141" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。</t>
+      </text>
+    </comment>
+    <comment ref="K142" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。</t>
+      </text>
+    </comment>
+    <comment ref="K143" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 汇丰投资基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K144" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 汇丰投资基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K145" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 汇丰投资基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K146" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 汇丰投资基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K147" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 汇丰投资基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K148" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 汇丰投资基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K149" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 东方汇理(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K150" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 东方汇理(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K151" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 东方汇理(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K152" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 东方汇理(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K153" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 东方汇理(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K154" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 东方汇理(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K155" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 东方汇理(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K156" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 东方汇理(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K157" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 中银保诚资管
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K158" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 摩根基金(亚洲)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K159" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 摩根基金(亚洲)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K160" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 摩根基金(亚洲)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K161" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 摩根基金(亚洲)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K162" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 摩根基金(亚洲)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K163" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 摩根基金(亚洲)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K164" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 摩根基金(亚洲)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K165" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 摩根基金(亚洲)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K166" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 摩根基金(亚洲)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K167" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 安联环球投资(亚太)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K168" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 安联环球投资(亚太)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K169" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 安联环球投资(亚太)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K170" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 安联环球投资(亚太)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K171" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 安联环球投资(亚太)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K172" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 安联环球投资(亚太)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K173" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 安联环球投资(亚太)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K174" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 安联环球投资(亚太)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K175" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 安联环球投资(亚太)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K176" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 安联环球投资(亚太)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K177" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 安联环球投资(亚太)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K178" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 安联环球投资(亚太)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K179" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 安联环球投资(亚太)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K180" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 安联环球投资(亚太)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K181" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 华夏基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K182" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 华夏基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K183" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 华夏基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K184" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 华夏基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K185" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 华夏基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K186" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 华夏基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K187" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 华夏基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K188" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 华夏基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K189" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 华夏基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K190" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 华夏基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K191" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 华夏基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K192" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 华夏基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K193" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 华夏基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K194" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 华夏基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K195" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 华夏基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K196" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 华夏基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K197" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 华夏基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K198" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 华夏基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K199" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 华夏基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K200" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 华夏基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K201" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 贝莱德资管(北亚)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K202" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 贝莱德资管(北亚)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K203" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 贝莱德资管(北亚)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K204" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 太平资管(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K205" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 易方达资管(香港)</t>
+      </text>
+    </comment>
+    <comment ref="K206" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 易方达资管(香港)</t>
+      </text>
+    </comment>
+    <comment ref="K207" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 易方达资管(香港)</t>
+      </text>
+    </comment>
+    <comment ref="K208" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 易方达资管(香港)</t>
+      </text>
+    </comment>
+    <comment ref="K209" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 易方达资管(香港)</t>
+      </text>
+    </comment>
+    <comment ref="K210" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 易方达资管(香港)</t>
+      </text>
+    </comment>
+    <comment ref="K211" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 易方达资管(香港)</t>
+      </text>
+    </comment>
+    <comment ref="K212" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 易方达资管(香港)</t>
+      </text>
+    </comment>
+    <comment ref="K213" authorId="0" shapeId="0">
+      <text>
+        <t>来源: 官网/财务报表自动抓取
+URL: https://www.efunds.com.hk/aboutus
+原币种: CNY
+上下文: a Assets Management Golden Shell Award Most competitive fund subsidiary——E Fund Management (HK) Co., Ltd Bloomberg Businessweek/Chinese Edition Top Fund Awards 2019 RMB Bond of Mutual Funds (Best Performer) (1 Year)——E Fund (HK) RMB Fixed Income Fund RMB Bond of Mutual Funds (Best Performer) (5 Years)——E Fund (HK) RMB Fixed In</t>
+      </text>
+    </comment>
+    <comment ref="K214" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 易方达资管(香港)</t>
+      </text>
+    </comment>
+    <comment ref="K215" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 富达基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K216" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 富达基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K217" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 富达基金(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K218" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 瑞银环球资管(香港)
+抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K219" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 瑞银环球资管(香港)
+抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K220" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 瑞银环球资管(香港)
+抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K221" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 瑞银环球资管(香港)
+抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K222" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 瑞银环球资管(香港)
+抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K223" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 瑞银环球资管(香港)
+抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K224" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 瑞银环球资管(香港)
+抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K225" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 瑞银环球资管(香港)
+抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K226" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 瑞银环球资管(香港)
+抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K227" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 瑞银环球资管(香港)
+抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K228" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 瑞银环球资管(香港)
+抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K229" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 瑞银环球资管(香港)
+抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K230" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 瑞银环球资管(香港)
+抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K231" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 瑞银环球资管(香港)
+抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K232" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 瑞银环球资管(香港)
+抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K233" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 瑞银环球资管(香港)
+抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K234" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 瑞银环球资管(香港)
+抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K235" authorId="0" shapeId="0">
+      <text>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 瑞银环球资管(香港)
+抓取信息: Link discovery failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | Fetch failed for https://www.ubs.com/hk/en/assetmanagement: 403 Client Error: Forbidden for url: https://www.ubs.com/hk/en/assetmanagement | No global fund AUM evidence extracted.</t>
+      </text>
+    </comment>
+    <comment ref="K236" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: No manager source configured for 惠理基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K34" authorId="0" shapeId="0">
+抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf</t>
+      </text>
+    </comment>
+    <comment ref="K237" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: No manager source configured for 惠理基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K35" authorId="0" shapeId="0">
+抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf</t>
+      </text>
+    </comment>
+    <comment ref="K238" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: No manager source configured for 惠理基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K36" authorId="0" shapeId="0">
+抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf</t>
+      </text>
+    </comment>
+    <comment ref="K239" authorId="0" shapeId="0">
+      <text>
+        <t>来源: 官网/财务报表自动抓取
+URL: https://www.valuepartners-group.com/en/products-services/funds/
+原币种: USD
+上下文: View Performance Download Factsheets Share Classes Currency Latest NAV Valuation date Morningstar Rating ISIN codes Bloomberg tickers Class A USD Unhedged Acc USD 19.70 27-04-2026 HK0000352374 VPUSUAU HK 2026-04-29 11:02:21 Class A HKD Unhedged Acc HKD 19.82 27-04-2026 - HK0000352283 VPAHUAU HK 2026-04-29 11:02:21 Class A SGD H</t>
+      </text>
+    </comment>
+    <comment ref="K240" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: No manager source configured for 惠理基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K37" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
-      </text>
-    </comment>
-    <comment ref="K38" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
-      </text>
-    </comment>
-    <comment ref="K39" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
-      </text>
-    </comment>
-    <comment ref="K40" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
-      </text>
-    </comment>
-    <comment ref="K41" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
-      </text>
-    </comment>
-    <comment ref="K42" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
-      </text>
-    </comment>
-    <comment ref="K43" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
-      </text>
-    </comment>
-    <comment ref="K44" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
-      </text>
-    </comment>
-    <comment ref="K45" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
-      </text>
-    </comment>
-    <comment ref="K46" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
-      </text>
-    </comment>
-    <comment ref="K47" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
-      </text>
-    </comment>
-    <comment ref="K48" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
-      </text>
-    </comment>
-    <comment ref="K49" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 海通国际资管(香港)
-抓取信息: No manager source configured for 海通国际资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K50" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 博时基金(国际)
-抓取信息: No manager source configured for 博时基金(国际).</t>
-      </text>
-    </comment>
-    <comment ref="K51" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 博时基金(国际)
-抓取信息: No manager source configured for 博时基金(国际).</t>
-      </text>
-    </comment>
-    <comment ref="K52" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 博时基金(国际)
-抓取信息: No manager source configured for 博时基金(国际).</t>
-      </text>
-    </comment>
-    <comment ref="K53" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 博时基金(国际)
-抓取信息: No manager source configured for 博时基金(国际).</t>
-      </text>
-    </comment>
-    <comment ref="K54" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
-      </text>
-    </comment>
-    <comment ref="K55" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
-      </text>
-    </comment>
-    <comment ref="K56" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
-      </text>
-    </comment>
-    <comment ref="K57" authorId="0" shapeId="0">
+抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf</t>
+      </text>
+    </comment>
+    <comment ref="K241" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: No manager source configured for 惠理基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K58" authorId="0" shapeId="0">
+抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf</t>
+      </text>
+    </comment>
+    <comment ref="K242" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: No manager source configured for 惠理基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K59" authorId="0" shapeId="0">
+抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf</t>
+      </text>
+    </comment>
+    <comment ref="K243" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: No manager source configured for 惠理基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K60" authorId="0" shapeId="0">
+抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf</t>
+      </text>
+    </comment>
+    <comment ref="K244" authorId="0" shapeId="0">
+      <text>
+        <t>来源: 官网/财务报表自动抓取
+URL: https://www.valuepartners-group.com/en/products-services/funds/
+原币种: USD
+上下文: View Performance Download Factsheets Share Classes Currency Latest NAV Valuation date Morningstar Rating ISIN codes Bloomberg tickers Class A USD Unhedged Acc USD 19.70 27-04-2026 HK0000352374 VPUSUAU HK 2026-04-29 11:02:21 Class A HKD Unhedged Acc HKD 19.82 27-04-2026 - HK0000352283 VPAHUAU HK 2026-04-29 11:02:21 Class A SGD H</t>
+      </text>
+    </comment>
+    <comment ref="K245" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: No manager source configured for 惠理基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K61" authorId="0" shapeId="0">
+抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf</t>
+      </text>
+    </comment>
+    <comment ref="K246" authorId="0" shapeId="0">
+      <text>
+        <t>来源: 官网/财务报表自动抓取
+URL: https://www.valuepartners-group.com/en/products-services/funds/
+原币种: USD
+上下文: View Performance Download Factsheets Share Classes Currency Latest NAV Valuation date Morningstar Rating ISIN codes Bloomberg tickers Class A USD Unhedged Acc USD 19.70 27-04-2026 HK0000352374 VPUSUAU HK 2026-04-29 11:02:21 Class A HKD Unhedged Acc HKD 19.82 27-04-2026 - HK0000352283 VPAHUAU HK 2026-04-29 11:02:21 Class A SGD H</t>
+      </text>
+    </comment>
+    <comment ref="K247" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: No manager source configured for 惠理基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K62" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
-      </text>
-    </comment>
-    <comment ref="K63" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
-      </text>
-    </comment>
-    <comment ref="K64" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
-      </text>
-    </comment>
-    <comment ref="K65" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。</t>
-      </text>
-    </comment>
-    <comment ref="K66" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。</t>
-      </text>
-    </comment>
-    <comment ref="K67" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 东方汇理(香港)
-抓取信息: No manager source configured for 东方汇理(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K68" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 东方汇理(香港)
-抓取信息: No manager source configured for 东方汇理(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K69" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K70" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K71" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K72" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K73" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K74" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K75" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K76" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K77" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K78" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K79" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K80" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K81" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K82" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K83" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K84" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K85" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K86" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K87" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K88" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K89" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K90" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K91" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K92" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K93" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K94" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K95" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K96" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 海通国际资管(香港)
-抓取信息: No manager source configured for 海通国际资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K97" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 海通国际资管(香港)
-抓取信息: No manager source configured for 海通国际资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K98" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 华夏基金(香港)
-抓取信息: No manager source configured for 华夏基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K99" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 华夏基金(香港)
-抓取信息: No manager source configured for 华夏基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K100" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 华夏基金(香港)
-抓取信息: No manager source configured for 华夏基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K101" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 易方达资管(香港)
-抓取信息: No manager source configured for 易方达资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K102" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 易方达资管(香港)
-抓取信息: No manager source configured for 易方达资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K103" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 易方达资管(香港)
-抓取信息: No manager source configured for 易方达资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K104" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 弘收资管(香港)
-抓取信息: No manager source configured for 弘收资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K105" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 弘收资管(香港)
-抓取信息: No manager source configured for 弘收资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K106" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 弘收资管(香港)
-抓取信息: No manager source configured for 弘收资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K107" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 弘收资管(香港)
-抓取信息: No manager source configured for 弘收资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K108" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 高腾国际资管
-抓取信息: No manager source configured for 高腾国际资管.</t>
-      </text>
-    </comment>
-    <comment ref="K109" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 高腾国际资管
-抓取信息: No manager source configured for 高腾国际资管.</t>
-      </text>
-    </comment>
-    <comment ref="K110" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 高腾国际资管
-抓取信息: No manager source configured for 高腾国际资管.</t>
-      </text>
-    </comment>
-    <comment ref="K111" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 高腾国际资管
-抓取信息: No manager source configured for 高腾国际资管.</t>
-      </text>
-    </comment>
-    <comment ref="K112" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 东亚联丰投资管理
-抓取信息: No manager source configured for 东亚联丰投资管理.</t>
-      </text>
-    </comment>
-    <comment ref="K113" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 东亚联丰投资管理
-抓取信息: No manager source configured for 东亚联丰投资管理.</t>
-      </text>
-    </comment>
-    <comment ref="K114" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 东亚联丰投资管理
-抓取信息: No manager source configured for 东亚联丰投资管理.</t>
-      </text>
-    </comment>
-    <comment ref="K115" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 兴证国际资管
-抓取信息: No manager source configured for 兴证国际资管.</t>
-      </text>
-    </comment>
-    <comment ref="K116" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 高腾国际资管
-抓取信息: No manager source configured for 高腾国际资管.</t>
-      </text>
-    </comment>
-    <comment ref="K117" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 高腾国际资管
-抓取信息: No manager source configured for 高腾国际资管.</t>
-      </text>
-    </comment>
-    <comment ref="K118" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 瑞银基金(卢森堡)
-抓取信息: No manager source configured for 瑞银基金(卢森堡).</t>
-      </text>
-    </comment>
-    <comment ref="K119" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 中银香港资管
-抓取信息: No manager source configured for 中银香港资管.</t>
-      </text>
-    </comment>
-    <comment ref="K120" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 南方东英资管
-抓取信息: No manager source configured for 南方东英资管.</t>
-      </text>
-    </comment>
-    <comment ref="K121" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 中银香港资管
-抓取信息: No manager source configured for 中银香港资管.</t>
-      </text>
-    </comment>
-    <comment ref="K122" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 中银香港资管
-抓取信息: No manager source configured for 中银香港资管.</t>
-      </text>
-    </comment>
-    <comment ref="K123" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 东亚联丰投资管理
-抓取信息: No manager source configured for 东亚联丰投资管理.</t>
-      </text>
-    </comment>
-    <comment ref="K124" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 东亚联丰投资管理
-抓取信息: No manager source configured for 东亚联丰投资管理.</t>
-      </text>
-    </comment>
-    <comment ref="K125" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根资管(亚太)
-抓取信息: No manager source configured for 摩根资管(亚太).</t>
-      </text>
-    </comment>
-    <comment ref="K126" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根资管(亚太)
-抓取信息: No manager source configured for 摩根资管(亚太).</t>
-      </text>
-    </comment>
-    <comment ref="K127" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根资管(亚太)
-抓取信息: No manager source configured for 摩根资管(亚太).</t>
-      </text>
-    </comment>
-    <comment ref="K128" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
-      </text>
-    </comment>
-    <comment ref="K129" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
-      </text>
-    </comment>
-    <comment ref="K130" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
-      </text>
-    </comment>
-    <comment ref="K131" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 施罗德投资管理(香港)
-抓取信息: No manager source configured for 施罗德投资管理(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K132" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 施罗德投资管理(香港)
-抓取信息: No manager source configured for 施罗德投资管理(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K133" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 施罗德投资管理(香港)
-抓取信息: No manager source configured for 施罗德投资管理(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K134" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。</t>
-      </text>
-    </comment>
-    <comment ref="K135" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 东亚联丰投资管理
-抓取信息: No manager source configured for 东亚联丰投资管理.</t>
-      </text>
-    </comment>
-    <comment ref="K136" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 东亚联丰投资管理
-抓取信息: No manager source configured for 东亚联丰投资管理.</t>
-      </text>
-    </comment>
-    <comment ref="K137" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 东方汇理(香港)
-抓取信息: No manager source configured for 东方汇理(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K138" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 东方汇理(香港)
-抓取信息: No manager source configured for 东方汇理(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K139" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 东方汇理(香港)
-抓取信息: No manager source configured for 东方汇理(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K140" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 东方汇理(香港)
-抓取信息: No manager source configured for 东方汇理(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K141" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。</t>
-      </text>
-    </comment>
-    <comment ref="K142" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。</t>
-      </text>
-    </comment>
-    <comment ref="K143" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K144" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K145" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K146" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K147" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K148" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 汇丰投资基金(香港)
-抓取信息: No manager source configured for 汇丰投资基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K149" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 东方汇理(香港)
-抓取信息: No manager source configured for 东方汇理(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K150" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 东方汇理(香港)
-抓取信息: No manager source configured for 东方汇理(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K151" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 东方汇理(香港)
-抓取信息: No manager source configured for 东方汇理(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K152" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 东方汇理(香港)
-抓取信息: No manager source configured for 东方汇理(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K153" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 东方汇理(香港)
-抓取信息: No manager source configured for 东方汇理(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K154" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 东方汇理(香港)
-抓取信息: No manager source configured for 东方汇理(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K155" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 东方汇理(香港)
-抓取信息: No manager source configured for 东方汇理(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K156" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 东方汇理(香港)
-抓取信息: No manager source configured for 东方汇理(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K157" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 中银保诚资管
-抓取信息: No manager source configured for 中银保诚资管.</t>
-      </text>
-    </comment>
-    <comment ref="K158" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
-      </text>
-    </comment>
-    <comment ref="K159" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
-      </text>
-    </comment>
-    <comment ref="K160" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
-      </text>
-    </comment>
-    <comment ref="K161" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
-      </text>
-    </comment>
-    <comment ref="K162" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
-      </text>
-    </comment>
-    <comment ref="K163" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
-      </text>
-    </comment>
-    <comment ref="K164" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
-      </text>
-    </comment>
-    <comment ref="K165" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
-      </text>
-    </comment>
-    <comment ref="K166" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No manager source configured for 摩根基金(亚洲).</t>
-      </text>
-    </comment>
-    <comment ref="K167" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 安联环球投资(亚太)
-抓取信息: No manager source configured for 安联环球投资(亚太).</t>
-      </text>
-    </comment>
-    <comment ref="K168" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 安联环球投资(亚太)
-抓取信息: No manager source configured for 安联环球投资(亚太).</t>
-      </text>
-    </comment>
-    <comment ref="K169" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 安联环球投资(亚太)
-抓取信息: No manager source configured for 安联环球投资(亚太).</t>
-      </text>
-    </comment>
-    <comment ref="K170" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 安联环球投资(亚太)
-抓取信息: No manager source configured for 安联环球投资(亚太).</t>
-      </text>
-    </comment>
-    <comment ref="K171" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 安联环球投资(亚太)
-抓取信息: No manager source configured for 安联环球投资(亚太).</t>
-      </text>
-    </comment>
-    <comment ref="K172" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 安联环球投资(亚太)
-抓取信息: No manager source configured for 安联环球投资(亚太).</t>
-      </text>
-    </comment>
-    <comment ref="K173" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 安联环球投资(亚太)
-抓取信息: No manager source configured for 安联环球投资(亚太).</t>
-      </text>
-    </comment>
-    <comment ref="K174" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 安联环球投资(亚太)
-抓取信息: No manager source configured for 安联环球投资(亚太).</t>
-      </text>
-    </comment>
-    <comment ref="K175" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 安联环球投资(亚太)
-抓取信息: No manager source configured for 安联环球投资(亚太).</t>
-      </text>
-    </comment>
-    <comment ref="K176" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 安联环球投资(亚太)
-抓取信息: No manager source configured for 安联环球投资(亚太).</t>
-      </text>
-    </comment>
-    <comment ref="K177" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 安联环球投资(亚太)
-抓取信息: No manager source configured for 安联环球投资(亚太).</t>
-      </text>
-    </comment>
-    <comment ref="K178" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 安联环球投资(亚太)
-抓取信息: No manager source configured for 安联环球投资(亚太).</t>
-      </text>
-    </comment>
-    <comment ref="K179" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 安联环球投资(亚太)
-抓取信息: No manager source configured for 安联环球投资(亚太).</t>
-      </text>
-    </comment>
-    <comment ref="K180" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 安联环球投资(亚太)
-抓取信息: No manager source configured for 安联环球投资(亚太).</t>
-      </text>
-    </comment>
-    <comment ref="K181" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 华夏基金(香港)
-抓取信息: No manager source configured for 华夏基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K182" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 华夏基金(香港)
-抓取信息: No manager source configured for 华夏基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K183" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 华夏基金(香港)
-抓取信息: No manager source configured for 华夏基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K184" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 华夏基金(香港)
-抓取信息: No manager source configured for 华夏基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K185" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 华夏基金(香港)
-抓取信息: No manager source configured for 华夏基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K186" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 华夏基金(香港)
-抓取信息: No manager source configured for 华夏基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K187" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 华夏基金(香港)
-抓取信息: No manager source configured for 华夏基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K188" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 华夏基金(香港)
-抓取信息: No manager source configured for 华夏基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K189" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 华夏基金(香港)
-抓取信息: No manager source configured for 华夏基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K190" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 华夏基金(香港)
-抓取信息: No manager source configured for 华夏基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K191" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 华夏基金(香港)
-抓取信息: No manager source configured for 华夏基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K192" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 华夏基金(香港)
-抓取信息: No manager source configured for 华夏基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K193" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 华夏基金(香港)
-抓取信息: No manager source configured for 华夏基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K194" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 华夏基金(香港)
-抓取信息: No manager source configured for 华夏基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K195" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 华夏基金(香港)
-抓取信息: No manager source configured for 华夏基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K196" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 华夏基金(香港)
-抓取信息: No manager source configured for 华夏基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K197" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 华夏基金(香港)
-抓取信息: No manager source configured for 华夏基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K198" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 华夏基金(香港)
-抓取信息: No manager source configured for 华夏基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K199" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 华夏基金(香港)
-抓取信息: No manager source configured for 华夏基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K200" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 华夏基金(香港)
-抓取信息: No manager source configured for 华夏基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K201" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 贝莱德资管(北亚)
-抓取信息: No manager source configured for 贝莱德资管(北亚).</t>
-      </text>
-    </comment>
-    <comment ref="K202" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 贝莱德资管(北亚)
-抓取信息: No manager source configured for 贝莱德资管(北亚).</t>
-      </text>
-    </comment>
-    <comment ref="K203" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 贝莱德资管(北亚)
-抓取信息: No manager source configured for 贝莱德资管(北亚).</t>
-      </text>
-    </comment>
-    <comment ref="K204" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 太平资管(香港)
-抓取信息: No manager source configured for 太平资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K205" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 易方达资管(香港)
-抓取信息: No manager source configured for 易方达资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K206" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 易方达资管(香港)
-抓取信息: No manager source configured for 易方达资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K207" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 易方达资管(香港)
-抓取信息: No manager source configured for 易方达资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K208" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 易方达资管(香港)
-抓取信息: No manager source configured for 易方达资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K209" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 易方达资管(香港)
-抓取信息: No manager source configured for 易方达资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K210" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 易方达资管(香港)
-抓取信息: No manager source configured for 易方达资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K211" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 易方达资管(香港)
-抓取信息: No manager source configured for 易方达资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K212" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 易方达资管(香港)
-抓取信息: No manager source configured for 易方达资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K213" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 易方达资管(香港)
-抓取信息: No manager source configured for 易方达资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K214" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 易方达资管(香港)
-抓取信息: No manager source configured for 易方达资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K215" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 富达基金(香港)
-抓取信息: No manager source configured for 富达基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K216" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 富达基金(香港)
-抓取信息: No manager source configured for 富达基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K217" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 富达基金(香港)
-抓取信息: No manager source configured for 富达基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K218" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 瑞银环球资管(香港)
-抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K219" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 瑞银环球资管(香港)
-抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K220" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 瑞银环球资管(香港)
-抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K221" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 瑞银环球资管(香港)
-抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K222" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 瑞银环球资管(香港)
-抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K223" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 瑞银环球资管(香港)
-抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K224" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 瑞银环球资管(香港)
-抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K225" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 瑞银环球资管(香港)
-抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K226" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 瑞银环球资管(香港)
-抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K227" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 瑞银环球资管(香港)
-抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K228" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 瑞银环球资管(香港)
-抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K229" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 瑞银环球资管(香港)
-抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K230" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 瑞银环球资管(香港)
-抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K231" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 瑞银环球资管(香港)
-抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K232" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 瑞银环球资管(香港)
-抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K233" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 瑞银环球资管(香港)
-抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K234" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 瑞银环球资管(香港)
-抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K235" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 瑞银环球资管(香港)
-抓取信息: No manager source configured for 瑞银环球资管(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K236" authorId="0" shapeId="0">
+抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf</t>
+      </text>
+    </comment>
+    <comment ref="K248" authorId="0" shapeId="0">
+      <text>
+        <t>来源: 官网/财务报表自动抓取
+URL: https://www.valuepartners-group.com/en/products-services/funds/
+原币种: USD
+上下文: View Performance Download Factsheets Share Classes Currency Latest NAV Valuation date Morningstar Rating ISIN codes Bloomberg tickers Class A USD Unhedged Acc USD 19.70 27-04-2026 HK0000352374 VPUSUAU HK 2026-04-29 11:02:21 Class A HKD Unhedged Acc HKD 19.82 27-04-2026 - HK0000352283 VPAHUAU HK 2026-04-29 11:02:21 Class A SGD H</t>
+      </text>
+    </comment>
+    <comment ref="K249" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: No manager source configured for 惠理基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K237" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 惠理基金(香港)
-抓取信息: No manager source configured for 惠理基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K238" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 惠理基金(香港)
-抓取信息: No manager source configured for 惠理基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K239" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 惠理基金(香港)
-抓取信息: No manager source configured for 惠理基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K240" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 惠理基金(香港)
-抓取信息: No manager source configured for 惠理基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K241" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 惠理基金(香港)
-抓取信息: No manager source configured for 惠理基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K242" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 惠理基金(香港)
-抓取信息: No manager source configured for 惠理基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K243" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 惠理基金(香港)
-抓取信息: No manager source configured for 惠理基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K244" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 惠理基金(香港)
-抓取信息: No manager source configured for 惠理基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K245" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 惠理基金(香港)
-抓取信息: No manager source configured for 惠理基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K246" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 惠理基金(香港)
-抓取信息: No manager source configured for 惠理基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K247" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 惠理基金(香港)
-抓取信息: No manager source configured for 惠理基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K248" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 惠理基金(香港)
-抓取信息: No manager source configured for 惠理基金(香港).</t>
-      </text>
-    </comment>
-    <comment ref="K249" authorId="0" shapeId="0">
-      <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 惠理基金(香港)
-抓取信息: No manager source configured for 惠理基金(香港).</t>
+抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf</t>
       </text>
     </comment>
   </commentList>
@@ -3906,7 +3916,9 @@
       <c r="J16" s="2" t="n">
         <v>79.9375716</v>
       </c>
-      <c r="K16" s="3" t="n"/>
+      <c r="K16" s="4" t="n">
+        <v>1e-06</v>
+      </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
           <t>操礼艳,陈子栋,何民基,何佩诗,洪若甄,李多恩,罗景,苏俊祺,夏箐,谢清海,徐福宏,于霄,余辰俊,锺慧欣,锺民颕</t>
@@ -4893,7 +4905,9 @@
       <c r="J27" s="2" t="n">
         <v>134.94129444</v>
       </c>
-      <c r="K27" s="3" t="n"/>
+      <c r="K27" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
           <t>Cheah Hye Cheng,Ho Man Kei Norman,Hung Yeuk Yan Renee,So Chun Ki Louis,Chow Eric,Wang Alan,Ho Doris,Yu Michelle,何民基</t>
@@ -5332,7 +5346,9 @@
       <c r="J32" s="2" t="n">
         <v>267.38207352</v>
       </c>
-      <c r="K32" s="3" t="n"/>
+      <c r="K32" s="4" t="n">
+        <v>6.83901</v>
+      </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
           <t>蔡少俊,祁广东,杨洋</t>
@@ -9492,7 +9508,9 @@
       <c r="J33" s="2" t="n">
         <v>72.4668762</v>
       </c>
-      <c r="K33" s="3" t="n"/>
+      <c r="K33" s="4" t="n">
+        <v>1e-06</v>
+      </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
           <t>操礼艳,陈子栋,何民基,何佩诗,洪若甄,李多恩,罗景,苏俊祺,夏箐,谢清海,徐福宏,于霄,余辰俊,锺慧欣,锺民颕</t>
@@ -9585,7 +9603,9 @@
       <c r="J34" s="2" t="n">
         <v>72.4668762</v>
       </c>
-      <c r="K34" s="3" t="n"/>
+      <c r="K34" s="4" t="n">
+        <v>1e-06</v>
+      </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
           <t>操礼艳,陈子栋,何民基,何佩诗,洪若甄,李多恩,罗景,苏俊祺,夏箐,谢清海,徐福宏,于霄,余辰俊,锺慧欣,锺民颕</t>
@@ -9678,7 +9698,9 @@
       <c r="J35" s="2" t="n">
         <v>72.4668762</v>
       </c>
-      <c r="K35" s="3" t="n"/>
+      <c r="K35" s="4" t="n">
+        <v>1e-06</v>
+      </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
           <t>操礼艳,陈子栋,何民基,何佩诗,洪若甄,李多恩,罗景,苏俊祺,夏箐,谢清海,徐福宏,于霄,余辰俊,锺慧欣,锺民颕</t>
@@ -9769,7 +9791,9 @@
       <c r="J36" s="2" t="n">
         <v>72.4668762</v>
       </c>
-      <c r="K36" s="3" t="n"/>
+      <c r="K36" s="4" t="n">
+        <v>1e-06</v>
+      </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
           <t>操礼艳,陈子栋,何民基,何佩诗,洪若甄,李多恩,罗景,苏俊祺,夏箐,谢清海,徐福宏,于霄,余辰俊,锺慧欣,锺民颕</t>
@@ -11654,7 +11678,9 @@
       <c r="J57" s="2" t="n">
         <v>121.0964194</v>
       </c>
-      <c r="K57" s="3" t="n"/>
+      <c r="K57" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
           <t>Cheah Hye Cheng,Ho Man Kei Norman,Hung Yeuk Yan Renee,So Chun Ki Louis,Chow Eric,Wang Alan,Ho Doris,Yu Michelle,何民基</t>
@@ -11741,7 +11767,9 @@
       <c r="J58" s="2" t="n">
         <v>121.0964194</v>
       </c>
-      <c r="K58" s="3" t="n"/>
+      <c r="K58" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
           <t>Cheah Hye Cheng,Ho Man Kei Norman,Hung Yeuk Yan Renee,So Chun Ki Louis,Chow Eric,Wang Alan,Ho Doris,Yu Michelle,何民基</t>
@@ -11828,7 +11856,9 @@
       <c r="J59" s="2" t="n">
         <v>121.0964194</v>
       </c>
-      <c r="K59" s="3" t="n"/>
+      <c r="K59" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
           <t>Cheah Hye Cheng,Ho Man Kei Norman,Hung Yeuk Yan Renee,So Chun Ki Louis,Chow Eric,Wang Alan,Ho Doris,Yu Michelle,何民基</t>
@@ -11915,7 +11945,9 @@
       <c r="J60" s="2" t="n">
         <v>121.0964194</v>
       </c>
-      <c r="K60" s="3" t="n"/>
+      <c r="K60" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
           <t>Cheah Hye Cheng,Ho Man Kei Norman,Hung Yeuk Yan Renee,So Chun Ki Louis,Chow Eric,Wang Alan,Ho Doris,Yu Michelle,何民基</t>
@@ -12002,7 +12034,9 @@
       <c r="J61" s="2" t="n">
         <v>121.0964194</v>
       </c>
-      <c r="K61" s="3" t="n"/>
+      <c r="K61" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
           <t>Cheah Hye Cheng,Ho Man Kei Norman,Hung Yeuk Yan Renee,So Chun Ki Louis,Chow Eric,Wang Alan,Ho Doris,Yu Michelle,何民基</t>
@@ -25013,7 +25047,9 @@
       <c r="J213" s="2" t="n">
         <v>4.712567940256</v>
       </c>
-      <c r="K213" s="3" t="n"/>
+      <c r="K213" s="4" t="n">
+        <v>2e-05</v>
+      </c>
       <c r="L213" s="2" t="inlineStr">
         <is>
           <t>唐博伦</t>
@@ -27033,7 +27069,9 @@
       <c r="J239" s="2" t="n">
         <v>49.68285876</v>
       </c>
-      <c r="K239" s="3" t="n"/>
+      <c r="K239" s="4" t="n">
+        <v>1e-06</v>
+      </c>
       <c r="L239" s="2" t="inlineStr">
         <is>
           <t>Kelly Chung</t>
@@ -27420,7 +27458,9 @@
       <c r="J244" s="2" t="n">
         <v>49.68285876</v>
       </c>
-      <c r="K244" s="3" t="n"/>
+      <c r="K244" s="4" t="n">
+        <v>1e-06</v>
+      </c>
       <c r="L244" s="2" t="inlineStr">
         <is>
           <t>Kelly Chung</t>
@@ -27578,7 +27618,9 @@
       <c r="J246" s="2" t="n">
         <v>49.68285876</v>
       </c>
-      <c r="K246" s="3" t="n"/>
+      <c r="K246" s="4" t="n">
+        <v>1e-06</v>
+      </c>
       <c r="L246" s="2" t="inlineStr">
         <is>
           <t>Kelly Chung</t>
@@ -27736,7 +27778,9 @@
       <c r="J248" s="2" t="n">
         <v>49.68285876</v>
       </c>
-      <c r="K248" s="3" t="n"/>
+      <c r="K248" s="4" t="n">
+        <v>1e-06</v>
+      </c>
       <c r="L248" s="2" t="inlineStr">
         <is>
           <t>Kelly Chung</t>

--- a/outputs/northbound_aum_2026-04-29.xlsx
+++ b/outputs/northbound_aum_2026-04-29.xlsx
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,10 +39,6 @@
     <font>
       <name val="Arial"/>
       <color rgb="00000000"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00FF0000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -70,7 +66,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -81,7 +77,6 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -264,10 +259,9 @@
     </comment>
     <comment ref="K16" authorId="0" shapeId="0">
       <text>
-        <t>来源: 官网/财务报表自动抓取
-URL: https://www.valuepartners-group.com/en/products-services/funds/
-原币种: HKD
-上下文: iew Performance Download Factsheets Share Classes Currency Latest NAV Valuation date Morningstar Rating ISIN codes Bloomberg tickers Class A HKD HKD 105.63 27-04-2026 KYG9317M1033 VPCHIGC KY 2026-04-29 11:02:11 Class A USD USD 17.28 27-04-2026 KYG9317M1603 VPCHAUS KY 2026-04-29 11:02:16 Class A AUD Hedged AUD 15.90</t>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 惠理基金(香港)
+抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K17" authorId="0" shapeId="0">
@@ -342,10 +336,9 @@
     </comment>
     <comment ref="K27" authorId="0" shapeId="0">
       <text>
-        <t>来源: 官网/财务报表自动抓取
-URL: https://www.valuepartners-group.com/en/products-services/funds/
-原币种: EUR
-上下文: AD 3.16 27-04-2026 - KYG9319N2400 VPGCCAD KY 2026-04-29 11:03:33 Class A EUR Hedged MDis EUR 3.44 27-04-2026 - KYG9319N3499 VCHAMEH KY 2026-04-29 11:03:38 Class A EUR Hedged Acc EUR 6.80 27-04-2026 - KYG9319N3804 VPGAEHA KY 2026-04-29 11:03:37 Class A GBP He</t>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 惠理基金(香港)
+抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K28" authorId="0" shapeId="0">
@@ -376,10 +369,9 @@
     </comment>
     <comment ref="K32" authorId="0" shapeId="0">
       <text>
-        <t>来源: 官网/财务报表自动抓取
-URL: https://www.efunds.com.hk/aboutus
-原币种: USD
-上下文: Fund (HK) Select Bond Fund . Launched E Fund (HK) Greater China Leaders Fund . Launched E Fund (HK) Greater China Quality Growth Fund . 2013 Granted a quota of US$100 million by SAFE under the Qualified Foreign Institutional Investors (QFII) program. This made E Fund HK the first batch of wholly-owned subsidiaries of Chinese... Gran</t>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 易方达资管(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K33" authorId="0" shapeId="0">
@@ -702,34 +694,30 @@
     </comment>
     <comment ref="K33" authorId="0" shapeId="0">
       <text>
-        <t>来源: 官网/财务报表自动抓取
-URL: https://www.valuepartners-group.com/en/products-services/funds/
-原币种: HKD
-上下文: iew Performance Download Factsheets Share Classes Currency Latest NAV Valuation date Morningstar Rating ISIN codes Bloomberg tickers Class A HKD HKD 105.63 27-04-2026 KYG9317M1033 VPCHIGC KY 2026-04-29 11:02:11 Class A USD USD 17.28 27-04-2026 KYG9317M1603 VPCHAUS KY 2026-04-29 11:02:16 Class A AUD Hedged AUD 15.90</t>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 惠理基金(香港)
+抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K34" authorId="0" shapeId="0">
       <text>
-        <t>来源: 官网/财务报表自动抓取
-URL: https://www.valuepartners-group.com/en/products-services/funds/
-原币种: HKD
-上下文: iew Performance Download Factsheets Share Classes Currency Latest NAV Valuation date Morningstar Rating ISIN codes Bloomberg tickers Class A HKD HKD 105.63 27-04-2026 KYG9317M1033 VPCHIGC KY 2026-04-29 11:02:11 Class A USD USD 17.28 27-04-2026 KYG9317M1603 VPCHAUS KY 2026-04-29 11:02:16 Class A AUD Hedged AUD 15.90</t>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 惠理基金(香港)
+抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K35" authorId="0" shapeId="0">
       <text>
-        <t>来源: 官网/财务报表自动抓取
-URL: https://www.valuepartners-group.com/en/products-services/funds/
-原币种: HKD
-上下文: iew Performance Download Factsheets Share Classes Currency Latest NAV Valuation date Morningstar Rating ISIN codes Bloomberg tickers Class A HKD HKD 105.63 27-04-2026 KYG9317M1033 VPCHIGC KY 2026-04-29 11:02:11 Class A USD USD 17.28 27-04-2026 KYG9317M1603 VPCHAUS KY 2026-04-29 11:02:16 Class A AUD Hedged AUD 15.90</t>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 惠理基金(香港)
+抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K36" authorId="0" shapeId="0">
       <text>
-        <t>来源: 官网/财务报表自动抓取
-URL: https://www.valuepartners-group.com/en/products-services/funds/
-原币种: HKD
-上下文: iew Performance Download Factsheets Share Classes Currency Latest NAV Valuation date Morningstar Rating ISIN codes Bloomberg tickers Class A HKD HKD 105.63 27-04-2026 KYG9317M1033 VPCHIGC KY 2026-04-29 11:02:11 Class A USD USD 17.28 27-04-2026 KYG9317M1603 VPCHAUS KY 2026-04-29 11:02:16 Class A AUD Hedged AUD 15.90</t>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 惠理基金(香港)
+抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K37" authorId="0" shapeId="0">
@@ -874,42 +862,37 @@
     </comment>
     <comment ref="K57" authorId="0" shapeId="0">
       <text>
-        <t>来源: 官网/财务报表自动抓取
-URL: https://www.valuepartners-group.com/en/products-services/funds/
-原币种: EUR
-上下文: AD 3.16 27-04-2026 - KYG9319N2400 VPGCCAD KY 2026-04-29 11:03:33 Class A EUR Hedged MDis EUR 3.44 27-04-2026 - KYG9319N3499 VCHAMEH KY 2026-04-29 11:03:38 Class A EUR Hedged Acc EUR 6.80 27-04-2026 - KYG9319N3804 VPGAEHA KY 2026-04-29 11:03:37 Class A GBP He</t>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 惠理基金(香港)
+抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K58" authorId="0" shapeId="0">
       <text>
-        <t>来源: 官网/财务报表自动抓取
-URL: https://www.valuepartners-group.com/en/products-services/funds/
-原币种: EUR
-上下文: AD 3.16 27-04-2026 - KYG9319N2400 VPGCCAD KY 2026-04-29 11:03:33 Class A EUR Hedged MDis EUR 3.44 27-04-2026 - KYG9319N3499 VCHAMEH KY 2026-04-29 11:03:38 Class A EUR Hedged Acc EUR 6.80 27-04-2026 - KYG9319N3804 VPGAEHA KY 2026-04-29 11:03:37 Class A GBP He</t>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 惠理基金(香港)
+抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K59" authorId="0" shapeId="0">
       <text>
-        <t>来源: 官网/财务报表自动抓取
-URL: https://www.valuepartners-group.com/en/products-services/funds/
-原币种: EUR
-上下文: AD 3.16 27-04-2026 - KYG9319N2400 VPGCCAD KY 2026-04-29 11:03:33 Class A EUR Hedged MDis EUR 3.44 27-04-2026 - KYG9319N3499 VCHAMEH KY 2026-04-29 11:03:38 Class A EUR Hedged Acc EUR 6.80 27-04-2026 - KYG9319N3804 VPGAEHA KY 2026-04-29 11:03:37 Class A GBP He</t>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 惠理基金(香港)
+抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K60" authorId="0" shapeId="0">
       <text>
-        <t>来源: 官网/财务报表自动抓取
-URL: https://www.valuepartners-group.com/en/products-services/funds/
-原币种: EUR
-上下文: AD 3.16 27-04-2026 - KYG9319N2400 VPGCCAD KY 2026-04-29 11:03:33 Class A EUR Hedged MDis EUR 3.44 27-04-2026 - KYG9319N3499 VCHAMEH KY 2026-04-29 11:03:38 Class A EUR Hedged Acc EUR 6.80 27-04-2026 - KYG9319N3804 VPGAEHA KY 2026-04-29 11:03:37 Class A GBP He</t>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 惠理基金(香港)
+抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K61" authorId="0" shapeId="0">
       <text>
-        <t>来源: 官网/财务报表自动抓取
-URL: https://www.valuepartners-group.com/en/products-services/funds/
-原币种: EUR
-上下文: AD 3.16 27-04-2026 - KYG9319N2400 VPGCCAD KY 2026-04-29 11:03:33 Class A EUR Hedged MDis EUR 3.44 27-04-2026 - KYG9319N3499 VCHAMEH KY 2026-04-29 11:03:38 Class A EUR Hedged Acc EUR 6.80 27-04-2026 - KYG9319N3804 VPGAEHA KY 2026-04-29 11:03:37 Class A GBP He</t>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 惠理基金(香港)
+抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K62" authorId="0" shapeId="0">
@@ -1184,19 +1167,22 @@
     <comment ref="K101" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
-基金管理人: 易方达资管(香港)</t>
+基金管理人: 易方达资管(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K102" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
-基金管理人: 易方达资管(香港)</t>
+基金管理人: 易方达资管(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K103" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
-基金管理人: 易方达资管(香港)</t>
+基金管理人: 易方达资管(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K104" authorId="0" shapeId="0">
@@ -1903,63 +1889,71 @@
     <comment ref="K205" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
-基金管理人: 易方达资管(香港)</t>
+基金管理人: 易方达资管(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K206" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
-基金管理人: 易方达资管(香港)</t>
+基金管理人: 易方达资管(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K207" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
-基金管理人: 易方达资管(香港)</t>
+基金管理人: 易方达资管(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K208" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
-基金管理人: 易方达资管(香港)</t>
+基金管理人: 易方达资管(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K209" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
-基金管理人: 易方达资管(香港)</t>
+基金管理人: 易方达资管(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K210" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
-基金管理人: 易方达资管(香港)</t>
+基金管理人: 易方达资管(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K211" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
-基金管理人: 易方达资管(香港)</t>
+基金管理人: 易方达资管(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K212" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
-基金管理人: 易方达资管(香港)</t>
+基金管理人: 易方达资管(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K213" authorId="0" shapeId="0">
       <text>
-        <t>来源: 官网/财务报表自动抓取
-URL: https://www.efunds.com.hk/aboutus
-原币种: CNY
-上下文: a Assets Management Golden Shell Award Most competitive fund subsidiary——E Fund Management (HK) Co., Ltd Bloomberg Businessweek/Chinese Edition Top Fund Awards 2019 RMB Bond of Mutual Funds (Best Performer) (1 Year)——E Fund (HK) RMB Fixed Income Fund RMB Bond of Mutual Funds (Best Performer) (5 Years)——E Fund (HK) RMB Fixed In</t>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 易方达资管(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K214" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
-基金管理人: 易方达资管(香港)</t>
+基金管理人: 易方达资管(香港)
+抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K215" authorId="0" shapeId="0">
@@ -2113,102 +2107,98 @@
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf</t>
+抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K237" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf</t>
+抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K238" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf</t>
+抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K239" authorId="0" shapeId="0">
       <text>
-        <t>来源: 官网/财务报表自动抓取
-URL: https://www.valuepartners-group.com/en/products-services/funds/
-原币种: USD
-上下文: View Performance Download Factsheets Share Classes Currency Latest NAV Valuation date Morningstar Rating ISIN codes Bloomberg tickers Class A USD Unhedged Acc USD 19.70 27-04-2026 HK0000352374 VPUSUAU HK 2026-04-29 11:02:21 Class A HKD Unhedged Acc HKD 19.82 27-04-2026 - HK0000352283 VPAHUAU HK 2026-04-29 11:02:21 Class A SGD H</t>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 惠理基金(香港)
+抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K240" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf</t>
+抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K241" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf</t>
+抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K242" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf</t>
+抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K243" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf</t>
+抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K244" authorId="0" shapeId="0">
       <text>
-        <t>来源: 官网/财务报表自动抓取
-URL: https://www.valuepartners-group.com/en/products-services/funds/
-原币种: USD
-上下文: View Performance Download Factsheets Share Classes Currency Latest NAV Valuation date Morningstar Rating ISIN codes Bloomberg tickers Class A USD Unhedged Acc USD 19.70 27-04-2026 HK0000352374 VPUSUAU HK 2026-04-29 11:02:21 Class A HKD Unhedged Acc HKD 19.82 27-04-2026 - HK0000352283 VPAHUAU HK 2026-04-29 11:02:21 Class A SGD H</t>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 惠理基金(香港)
+抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K245" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf</t>
+抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K246" authorId="0" shapeId="0">
       <text>
-        <t>来源: 官网/财务报表自动抓取
-URL: https://www.valuepartners-group.com/en/products-services/funds/
-原币种: USD
-上下文: View Performance Download Factsheets Share Classes Currency Latest NAV Valuation date Morningstar Rating ISIN codes Bloomberg tickers Class A USD Unhedged Acc USD 19.70 27-04-2026 HK0000352374 VPUSUAU HK 2026-04-29 11:02:21 Class A HKD Unhedged Acc HKD 19.82 27-04-2026 - HK0000352283 VPAHUAU HK 2026-04-29 11:02:21 Class A SGD H</t>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 惠理基金(香港)
+抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K247" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf</t>
+抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K248" authorId="0" shapeId="0">
       <text>
-        <t>来源: 官网/财务报表自动抓取
-URL: https://www.valuepartners-group.com/en/products-services/funds/
-原币种: USD
-上下文: View Performance Download Factsheets Share Classes Currency Latest NAV Valuation date Morningstar Rating ISIN codes Bloomberg tickers Class A USD Unhedged Acc USD 19.70 27-04-2026 HK0000352374 VPUSUAU HK 2026-04-29 11:02:21 Class A HKD Unhedged Acc HKD 19.82 27-04-2026 - HK0000352283 VPAHUAU HK 2026-04-29 11:02:21 Class A SGD H</t>
+        <t>未抓到最新规模，单元格留空。
+基金管理人: 惠理基金(香港)
+抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K249" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 惠理基金(香港)
-抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf</t>
+抓取信息: Fetch failed for https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/ftp/files/reports/hdlv/001_fact_sheet/eng/hdlv_fact_sheet_2026-01-01_en.pdf | Fetch failed for https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf: 404 Client Error: Not Found for url: https://www.valuepartners-group.com/doc/notice/20170421_Notice_to_Investors_VP_Funds_Ongoing_Charges_E.pdf | No global fund AUM evidence extracted.</t>
       </text>
     </comment>
   </commentList>
@@ -3916,9 +3906,7 @@
       <c r="J16" s="2" t="n">
         <v>79.9375716</v>
       </c>
-      <c r="K16" s="4" t="n">
-        <v>1e-06</v>
-      </c>
+      <c r="K16" s="3" t="n"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
           <t>操礼艳,陈子栋,何民基,何佩诗,洪若甄,李多恩,罗景,苏俊祺,夏箐,谢清海,徐福宏,于霄,余辰俊,锺慧欣,锺民颕</t>
@@ -4905,9 +4893,7 @@
       <c r="J27" s="2" t="n">
         <v>134.94129444</v>
       </c>
-      <c r="K27" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="K27" s="3" t="n"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
           <t>Cheah Hye Cheng,Ho Man Kei Norman,Hung Yeuk Yan Renee,So Chun Ki Louis,Chow Eric,Wang Alan,Ho Doris,Yu Michelle,何民基</t>
@@ -5346,9 +5332,7 @@
       <c r="J32" s="2" t="n">
         <v>267.38207352</v>
       </c>
-      <c r="K32" s="4" t="n">
-        <v>6.83901</v>
-      </c>
+      <c r="K32" s="3" t="n"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
           <t>蔡少俊,祁广东,杨洋</t>
@@ -9508,9 +9492,7 @@
       <c r="J33" s="2" t="n">
         <v>72.4668762</v>
       </c>
-      <c r="K33" s="4" t="n">
-        <v>1e-06</v>
-      </c>
+      <c r="K33" s="3" t="n"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
           <t>操礼艳,陈子栋,何民基,何佩诗,洪若甄,李多恩,罗景,苏俊祺,夏箐,谢清海,徐福宏,于霄,余辰俊,锺慧欣,锺民颕</t>
@@ -9603,9 +9585,7 @@
       <c r="J34" s="2" t="n">
         <v>72.4668762</v>
       </c>
-      <c r="K34" s="4" t="n">
-        <v>1e-06</v>
-      </c>
+      <c r="K34" s="3" t="n"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
           <t>操礼艳,陈子栋,何民基,何佩诗,洪若甄,李多恩,罗景,苏俊祺,夏箐,谢清海,徐福宏,于霄,余辰俊,锺慧欣,锺民颕</t>
@@ -9698,9 +9678,7 @@
       <c r="J35" s="2" t="n">
         <v>72.4668762</v>
       </c>
-      <c r="K35" s="4" t="n">
-        <v>1e-06</v>
-      </c>
+      <c r="K35" s="3" t="n"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
           <t>操礼艳,陈子栋,何民基,何佩诗,洪若甄,李多恩,罗景,苏俊祺,夏箐,谢清海,徐福宏,于霄,余辰俊,锺慧欣,锺民颕</t>
@@ -9791,9 +9769,7 @@
       <c r="J36" s="2" t="n">
         <v>72.4668762</v>
       </c>
-      <c r="K36" s="4" t="n">
-        <v>1e-06</v>
-      </c>
+      <c r="K36" s="3" t="n"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
           <t>操礼艳,陈子栋,何民基,何佩诗,洪若甄,李多恩,罗景,苏俊祺,夏箐,谢清海,徐福宏,于霄,余辰俊,锺慧欣,锺民颕</t>
@@ -11678,9 +11654,7 @@
       <c r="J57" s="2" t="n">
         <v>121.0964194</v>
       </c>
-      <c r="K57" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="K57" s="3" t="n"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
           <t>Cheah Hye Cheng,Ho Man Kei Norman,Hung Yeuk Yan Renee,So Chun Ki Louis,Chow Eric,Wang Alan,Ho Doris,Yu Michelle,何民基</t>
@@ -11767,9 +11741,7 @@
       <c r="J58" s="2" t="n">
         <v>121.0964194</v>
       </c>
-      <c r="K58" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="K58" s="3" t="n"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
           <t>Cheah Hye Cheng,Ho Man Kei Norman,Hung Yeuk Yan Renee,So Chun Ki Louis,Chow Eric,Wang Alan,Ho Doris,Yu Michelle,何民基</t>
@@ -11856,9 +11828,7 @@
       <c r="J59" s="2" t="n">
         <v>121.0964194</v>
       </c>
-      <c r="K59" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="K59" s="3" t="n"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
           <t>Cheah Hye Cheng,Ho Man Kei Norman,Hung Yeuk Yan Renee,So Chun Ki Louis,Chow Eric,Wang Alan,Ho Doris,Yu Michelle,何民基</t>
@@ -11945,9 +11915,7 @@
       <c r="J60" s="2" t="n">
         <v>121.0964194</v>
       </c>
-      <c r="K60" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="K60" s="3" t="n"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
           <t>Cheah Hye Cheng,Ho Man Kei Norman,Hung Yeuk Yan Renee,So Chun Ki Louis,Chow Eric,Wang Alan,Ho Doris,Yu Michelle,何民基</t>
@@ -12034,9 +12002,7 @@
       <c r="J61" s="2" t="n">
         <v>121.0964194</v>
       </c>
-      <c r="K61" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="K61" s="3" t="n"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
           <t>Cheah Hye Cheng,Ho Man Kei Norman,Hung Yeuk Yan Renee,So Chun Ki Louis,Chow Eric,Wang Alan,Ho Doris,Yu Michelle,何民基</t>
@@ -25047,9 +25013,7 @@
       <c r="J213" s="2" t="n">
         <v>4.712567940256</v>
       </c>
-      <c r="K213" s="4" t="n">
-        <v>2e-05</v>
-      </c>
+      <c r="K213" s="3" t="n"/>
       <c r="L213" s="2" t="inlineStr">
         <is>
           <t>唐博伦</t>
@@ -27069,9 +27033,7 @@
       <c r="J239" s="2" t="n">
         <v>49.68285876</v>
       </c>
-      <c r="K239" s="4" t="n">
-        <v>1e-06</v>
-      </c>
+      <c r="K239" s="3" t="n"/>
       <c r="L239" s="2" t="inlineStr">
         <is>
           <t>Kelly Chung</t>
@@ -27458,9 +27420,7 @@
       <c r="J244" s="2" t="n">
         <v>49.68285876</v>
       </c>
-      <c r="K244" s="4" t="n">
-        <v>1e-06</v>
-      </c>
+      <c r="K244" s="3" t="n"/>
       <c r="L244" s="2" t="inlineStr">
         <is>
           <t>Kelly Chung</t>
@@ -27618,9 +27578,7 @@
       <c r="J246" s="2" t="n">
         <v>49.68285876</v>
       </c>
-      <c r="K246" s="4" t="n">
-        <v>1e-06</v>
-      </c>
+      <c r="K246" s="3" t="n"/>
       <c r="L246" s="2" t="inlineStr">
         <is>
           <t>Kelly Chung</t>
@@ -27778,9 +27736,7 @@
       <c r="J248" s="2" t="n">
         <v>49.68285876</v>
       </c>
-      <c r="K248" s="4" t="n">
-        <v>1e-06</v>
-      </c>
+      <c r="K248" s="3" t="n"/>
       <c r="L248" s="2" t="inlineStr">
         <is>
           <t>Kelly Chung</t>

--- a/outputs/northbound_aum_2026-04-29.xlsx
+++ b/outputs/northbound_aum_2026-04-29.xlsx
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,6 +39,10 @@
     <font>
       <name val="Arial"/>
       <color rgb="00000000"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00FF0000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -66,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -77,6 +81,7 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -217,16 +222,18 @@
     </comment>
     <comment ref="K10" authorId="0" shapeId="0">
       <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+        <t>来源: 官网/财务报表自动抓取
+URL: https://am.jpmorgan.com/content/dam/jpm-am-aem/asiapacific/hk/en/literature/fact-sheet/jpmorgan_asian_total_return_bond_e.pdf
+原币种: USD
+上下文: other debt securities. Expertise Fund Manager Julio Callegari, Jason Pang, Selina Yu Fund Information ((mth) - USD) Fund base currency USD Total fund size (m) USD 2,963.9 SEDOL B42HMC2 ISIN code HK0000055597 Bloomberg code JFASTRE HK Current charge Initial : 3.0% of NAV Redemption : 0% Management fee : 1.0% p.a. Denominated curre</t>
       </text>
     </comment>
     <comment ref="K11" authorId="0" shapeId="0">
       <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+        <t>来源: 官网/财务报表自动抓取
+URL: https://am.jpmorgan.com/content/dam/jpm-am-aem/asiapacific/hk/en/literature/fact-sheet/jpmorgan_pacific_securities_e.pdf
+原币种: USD
+上下文: g Japan, Australia and New Zealand. Expertise Fund Manager Robert Lloyd, Chun Yu Wong Fund Information ((acc) - USD) Fund base currency USD Total fund size (m) USD 810.8 SEDOL B42GYV2 ISIN code HK0000055746 Bloomberg code JFPACSI HK Current charge Initial : 5.0% of NAV Redemption : 0% Management fee : 1.5% p.a. Denominated curre</t>
       </text>
     </comment>
     <comment ref="K12" authorId="0" shapeId="0">
@@ -287,16 +294,18 @@
     </comment>
     <comment ref="K20" authorId="0" shapeId="0">
       <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+        <t>来源: 官网/财务报表自动抓取
+URL: https://am.jpmorgan.com/content/dam/jpm-am-aem/asiapacific/hk/en/literature/fact-sheet/jpmorgan_asia_equity_dividend_e.pdf
+原币种: USD
+上下文: ent manager expects to pay dividends. Expertise Fund Manager Julie Ho, Ruben Lienhard Fund Information ((mth) - USD) Fund base currency USD Total fund size (m) USD 3,056.8 SEDOL BBMT4W1 ISIN code HK0000151891 Bloomberg code JPAEDUS HK Current charge Initial : 5.0% of NAV Redemption : 0% Management fee : 1.5% p.a. Denominated curre</t>
       </text>
     </comment>
     <comment ref="K21" authorId="0" shapeId="0">
       <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+        <t>来源: 官网/财务报表自动抓取
+URL: https://am.jpmorgan.com/content/dam/jpm-am-aem/asiapacific/hk/en/literature/fact-sheet/jpmorgan_global_bond_e.pdf
+原币种: USD
+上下文: global investment grade debt securities. Expertise Fund Manager Arjun Vij, Jason Pang Fund Information ((san) - USD) Fund base currency USD Total fund size (m) USD 3,703.5 SEDOL B42HQ19 ISIN code HK0000055654 Bloomberg code JFGLBTI HK Current charge Initial : 3.0% of NAV Redemption : 0% Management fee : 0.8% p.a. Denominated curre</t>
       </text>
     </comment>
     <comment ref="K22" authorId="0" shapeId="0">
@@ -308,9 +317,10 @@
     </comment>
     <comment ref="K23" authorId="0" shapeId="0">
       <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+        <t>来源: 官网/财务报表自动抓取
+URL: https://am.jpmorgan.com/content/dam/jpm-am-aem/asiapacific/hk/en/literature/fact-sheet/jpmorgan_pacific_tech_e.pdf
+原币种: USD
+上下文: he Pacific region, including Japan. Expertise Fund Manager Oliver Cox, Ruben Lienhard Fund Information ((acc) - USD) Fund base currency USD Total fund size (m) USD 1,050.0 SEDOL B42H374 ISIN code HK0000055761 Bloomberg code JFPTECI HK Current charge Initial : 5.0% of NAV Redemption : 0% Management fee : 1.5% p.a. Denominated curre</t>
       </text>
     </comment>
     <comment ref="K24" authorId="0" shapeId="0">
@@ -322,9 +332,10 @@
     </comment>
     <comment ref="K25" authorId="0" shapeId="0">
       <text>
-        <t>未抓到最新规模，单元格留空。
-基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+        <t>来源: 官网/财务报表自动抓取
+URL: https://am.jpmorgan.com/content/dam/jpm-am-aem/asiapacific/hk/en/literature/fact-sheet/jpmorgan_asia_growth_e.pdf
+原币种: USD
+上下文: ed to, the growth in Asian economies. Expertise Fund Manager Joanna Kwok, Mark Davids Fund Information ((acc) - USD) Fund base currency USD Total fund size (m) USD 675.6 SEDOL B1XDC06 ISIN code HK0000038148 Bloomberg code JFASDOM HK Current charge Initial : 5.0% of NAV Redemption : 0% Management fee : 1.5% p.a. Denominated curre</t>
       </text>
     </comment>
     <comment ref="K26" authorId="0" shapeId="0">
@@ -434,7 +445,7 @@
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根资管(亚太)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: Fetch failed for https://am.jpmorgan.com/content/dam/jpm-am-aem/asiapacific/hk/en/literature/fact-sheet/jpmorgan_sar_hong_kong_e.pdf: 404 Client Error: Not Found for url: https://am.jpmorgan.com/content/dam/jpm-am-aem/asiapacific/hk/en/literature/fact-sheet/jpmorgan_sar_hong_kong_e.pdf | No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K42" authorId="0" shapeId="0">
@@ -479,28 +490,28 @@
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K3" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K5" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K6" authorId="0" shapeId="0">
@@ -535,14 +546,14 @@
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K11" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K12" authorId="0" shapeId="0">
@@ -724,84 +735,84 @@
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K38" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K39" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K40" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K41" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K42" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K43" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K44" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K45" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K46" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K47" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K48" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K49" authorId="0" shapeId="0">
@@ -843,21 +854,21 @@
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K55" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K56" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K57" authorId="0" shapeId="0">
@@ -899,21 +910,21 @@
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K63" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K64" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K65" authorId="0" shapeId="0">
@@ -1336,42 +1347,42 @@
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根资管(亚太)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: Fetch failed for https://am.jpmorgan.com/content/dam/jpm-am-aem/asiapacific/hk/en/literature/fact-sheet/jpmorgan_sar_hong_kong_e.pdf: 404 Client Error: Not Found for url: https://am.jpmorgan.com/content/dam/jpm-am-aem/asiapacific/hk/en/literature/fact-sheet/jpmorgan_sar_hong_kong_e.pdf | No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K126" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根资管(亚太)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: Fetch failed for https://am.jpmorgan.com/content/dam/jpm-am-aem/asiapacific/hk/en/literature/fact-sheet/jpmorgan_sar_hong_kong_e.pdf: 404 Client Error: Not Found for url: https://am.jpmorgan.com/content/dam/jpm-am-aem/asiapacific/hk/en/literature/fact-sheet/jpmorgan_sar_hong_kong_e.pdf | No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K127" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根资管(亚太)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: Fetch failed for https://am.jpmorgan.com/content/dam/jpm-am-aem/asiapacific/hk/en/literature/fact-sheet/jpmorgan_sar_hong_kong_e.pdf: 404 Client Error: Not Found for url: https://am.jpmorgan.com/content/dam/jpm-am-aem/asiapacific/hk/en/literature/fact-sheet/jpmorgan_sar_hong_kong_e.pdf | No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K128" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K129" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K130" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K131" authorId="0" shapeId="0">
@@ -1561,63 +1572,63 @@
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K159" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K160" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K161" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K162" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K163" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K164" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K165" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K166" authorId="0" shapeId="0">
       <text>
         <t>未抓到最新规模，单元格留空。
 基金管理人: 摩根基金(亚洲)
-抓取信息: No global fund AUM evidence extracted. | No mainland share-class AUM evidence extracted.</t>
+抓取信息: No mainland share-class AUM evidence extracted.</t>
       </text>
     </comment>
     <comment ref="K167" authorId="0" shapeId="0">
@@ -3376,7 +3387,9 @@
       <c r="J10" s="2" t="n">
         <v>205.1814078</v>
       </c>
-      <c r="K10" s="3" t="n"/>
+      <c r="K10" s="4" t="n">
+        <v>202.701409</v>
+      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t>彭逸升,Julio Callegari,余佩玲</t>
@@ -3467,7 +3480,9 @@
       <c r="J11" s="2" t="n">
         <v>56.13075468</v>
       </c>
-      <c r="K11" s="3" t="n"/>
+      <c r="K11" s="4" t="n">
+        <v>55.450691</v>
+      </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
           <t>Robert Lloyd,Julian Wong</t>
@@ -4264,7 +4279,9 @@
       <c r="J20" s="2" t="n">
         <v>211.61545812</v>
       </c>
-      <c r="K20" s="3" t="n"/>
+      <c r="K20" s="4" t="n">
+        <v>209.054849</v>
+      </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
           <t>Ruben Lienhard,何世宁</t>
@@ -4355,7 +4372,9 @@
       <c r="J21" s="2" t="n">
         <v>256.38451344</v>
       </c>
-      <c r="K21" s="3" t="n"/>
+      <c r="K21" s="4" t="n">
+        <v>253.282725</v>
+      </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
           <t>Arjun Vij,彭逸升</t>
@@ -4537,7 +4556,9 @@
       <c r="J23" s="2" t="n">
         <v>72.6859386</v>
       </c>
-      <c r="K23" s="3" t="n"/>
+      <c r="K23" s="4" t="n">
+        <v>71.809602</v>
+      </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
           <t>Oliver Cox,郭为熹</t>
@@ -4715,7 +4736,9 @@
       <c r="J25" s="2" t="n">
         <v>46.77112908</v>
       </c>
-      <c r="K25" s="3" t="n"/>
+      <c r="K25" s="4" t="n">
+        <v>46.20435</v>
+      </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
           <t>Mark Davids,郭为熹</t>
